--- a/Excel/UnionKeJiConfig.xlsx
+++ b/Excel/UnionKeJiConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5444887D-44CE-476F-B8DF-D785122515C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365C261D-9EDD-490E-AE0A-EFA67AA4B52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnionKeJiProto" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -583,7 +583,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="299">
   <si>
     <t>Id</t>
   </si>
@@ -1245,6 +1245,280 @@
   </si>
   <si>
     <t>玩家技减10级</t>
+  </si>
+  <si>
+    <t>Experience Technology Level 1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Experience Technology Level 2</t>
+  </si>
+  <si>
+    <t>Experience Technology Level 3</t>
+  </si>
+  <si>
+    <t>Experience Technology Level 4</t>
+  </si>
+  <si>
+    <t>Experience Technology Level 5</t>
+  </si>
+  <si>
+    <t>Experience Technology Level 6</t>
+  </si>
+  <si>
+    <t>Experience Technology Level 7</t>
+  </si>
+  <si>
+    <t>Experience Technology Level 8</t>
+  </si>
+  <si>
+    <t>Experience Technology Level 9</t>
+  </si>
+  <si>
+    <t>Experience Technology Level 10</t>
+  </si>
+  <si>
+    <t>Experience Technology Level 0</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold technology level 4</t>
+  </si>
+  <si>
+    <t>Gold technology level 0</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold technology level 1</t>
+  </si>
+  <si>
+    <t>Gold technology level 2</t>
+  </si>
+  <si>
+    <t>Gold technology level 3</t>
+  </si>
+  <si>
+    <t>Gold technology level 5</t>
+  </si>
+  <si>
+    <t>Gold technology level 6</t>
+  </si>
+  <si>
+    <t>Gold technology level 7</t>
+  </si>
+  <si>
+    <t>Gold technology level 8</t>
+  </si>
+  <si>
+    <t>Gold technology level 9</t>
+  </si>
+  <si>
+    <t>Gold technology level 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster Damage Level 0 </t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster Damage Level 1</t>
+  </si>
+  <si>
+    <t>Monster Damage Level 2</t>
+  </si>
+  <si>
+    <t>Monster Damage Level 3</t>
+  </si>
+  <si>
+    <t>Monster Damage Level 4</t>
+  </si>
+  <si>
+    <t>Monster Damage Level 5</t>
+  </si>
+  <si>
+    <t>Monster Damage Level 6</t>
+  </si>
+  <si>
+    <t>Monster Damage Level 7</t>
+  </si>
+  <si>
+    <t>Monster Damage Level 8</t>
+  </si>
+  <si>
+    <t>Monster Damage Level 9</t>
+  </si>
+  <si>
+    <t>Monster Damage Level 10</t>
+  </si>
+  <si>
+    <t>Monster Skill Level 0</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster Skill Level 1</t>
+  </si>
+  <si>
+    <t>Monster Skill Level 2</t>
+  </si>
+  <si>
+    <t>Monster Skill Level 3</t>
+  </si>
+  <si>
+    <t>Monster Skill Level 4</t>
+  </si>
+  <si>
+    <t>Monster Skill Level 5</t>
+  </si>
+  <si>
+    <t>Monster Skill Level 6</t>
+  </si>
+  <si>
+    <t>Monster Skill Level 7</t>
+  </si>
+  <si>
+    <t>Monster Skill Level 8</t>
+  </si>
+  <si>
+    <t>Monster Skill Level 9</t>
+  </si>
+  <si>
+    <t>Monster Skill Level 10</t>
+  </si>
+  <si>
+    <t>Monster Arts Defence Level 0</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster Arts Defence Level 1</t>
+  </si>
+  <si>
+    <t>Monster Arts Defence Level 2</t>
+  </si>
+  <si>
+    <t>Monster Arts Defence Level 3</t>
+  </si>
+  <si>
+    <t>Monster Arts Defence Level 5</t>
+  </si>
+  <si>
+    <t>Monster Arts Defence Level 6</t>
+  </si>
+  <si>
+    <t>Monster Arts Defence Level 7</t>
+  </si>
+  <si>
+    <t>Monster Arts Defence Level 8</t>
+  </si>
+  <si>
+    <t>Monster Arts Defence Level 9</t>
+  </si>
+  <si>
+    <t>Monster Arts Defence Level 10</t>
+  </si>
+  <si>
+    <t>Monster Arts Defence Level 4</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player Defence level 0</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player Defence level 1</t>
+  </si>
+  <si>
+    <t>Player Defence level 2</t>
+  </si>
+  <si>
+    <t>Player Defence level 3</t>
+  </si>
+  <si>
+    <t>Player Defence level 4</t>
+  </si>
+  <si>
+    <t>Player Defence level 5</t>
+  </si>
+  <si>
+    <t>Player Defence level 6</t>
+  </si>
+  <si>
+    <t>Player Defence level 7</t>
+  </si>
+  <si>
+    <t>Player Defence level 8</t>
+  </si>
+  <si>
+    <t>Player Defence level 9</t>
+  </si>
+  <si>
+    <t>Player Defence level 10</t>
+  </si>
+  <si>
+    <t>Player Arts Defence level 0</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player Arts Defence level 1</t>
+  </si>
+  <si>
+    <t>Player Arts Defence level 2</t>
+  </si>
+  <si>
+    <t>Player Arts Defence level 3</t>
+  </si>
+  <si>
+    <t>Player Arts Defence level 4</t>
+  </si>
+  <si>
+    <t>Player Arts Defence level 5</t>
+  </si>
+  <si>
+    <t>Player Arts Defence level 6</t>
+  </si>
+  <si>
+    <t>Player Arts Defence level 7</t>
+  </si>
+  <si>
+    <t>Player Arts Defence level 8</t>
+  </si>
+  <si>
+    <t>Player Arts Defence level 9</t>
+  </si>
+  <si>
+    <t>Player Arts Defence level 10</t>
+  </si>
+  <si>
+    <t>Monster Defence Level 0</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster Defence Level 1</t>
+  </si>
+  <si>
+    <t>Monster Defence Level 2</t>
+  </si>
+  <si>
+    <t>Monster Defence Level 3</t>
+  </si>
+  <si>
+    <t>Monster Defence Level 4</t>
+  </si>
+  <si>
+    <t>Monster Defence Level 5</t>
+  </si>
+  <si>
+    <t>Monster Defence Level 6</t>
+  </si>
+  <si>
+    <t>Monster Defence Level 7</t>
+  </si>
+  <si>
+    <t>Monster Defence Level 8</t>
+  </si>
+  <si>
+    <t>Monster Defence Level 9</t>
+  </si>
+  <si>
+    <t>Monster Defence Level 10</t>
   </si>
 </sst>
 </file>
@@ -2614,25 +2888,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:IC93"/>
+  <dimension ref="C1:ID93"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="3" max="3" width="8.5" style="3" customWidth="1"/>
     <col min="4" max="4" width="17.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5" style="3" customWidth="1"/>
-    <col min="6" max="8" width="14.125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="19.75" style="3" customWidth="1"/>
-    <col min="10" max="10" width="16.5" style="3" customWidth="1"/>
-    <col min="11" max="11" width="21.25" style="3" customWidth="1"/>
-    <col min="12" max="12" width="24.875" style="3" customWidth="1"/>
-    <col min="13" max="237" width="8.875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="28.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="3" customWidth="1"/>
+    <col min="7" max="9" width="14.125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="19.75" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="3" customWidth="1"/>
+    <col min="12" max="12" width="21.25" style="3" customWidth="1"/>
+    <col min="13" max="13" width="24.875" style="3" customWidth="1"/>
+    <col min="14" max="238" width="8.875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:237" s="1" customFormat="1" ht="14.25"/>
-    <row r="2" spans="3:237" ht="13.5" customHeight="1">
+    <row r="1" spans="3:238" s="1" customFormat="1" ht="14.25"/>
+    <row r="2" spans="3:238" ht="13.5" customHeight="1">
       <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="3:237" ht="20.100000000000001" customHeight="1">
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2640,74 +2916,80 @@
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="4" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C4" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="M4" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="5" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>8</v>
@@ -2719,16 +3001,19 @@
         <v>8</v>
       </c>
       <c r="J5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C6" s="8">
         <v>10100</v>
       </c>
@@ -2736,29 +3021,32 @@
         <v>134</v>
       </c>
       <c r="E6" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F6" s="8">
+      <c r="G6" s="8">
         <v>10101</v>
       </c>
-      <c r="G6" s="10">
+      <c r="H6" s="10">
         <v>0</v>
       </c>
-      <c r="H6" s="10">
+      <c r="I6" s="10">
         <v>1</v>
       </c>
-      <c r="I6" s="10">
+      <c r="J6" s="10">
         <v>28800</v>
       </c>
-      <c r="J6" s="11">
+      <c r="K6" s="11">
         <v>1000000</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="L6" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="L6" s="10"/>
-    </row>
-    <row r="7" spans="3:237" ht="20.100000000000001" customHeight="1">
+      <c r="M6" s="10"/>
+    </row>
+    <row r="7" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C7" s="8">
         <v>10101</v>
       </c>
@@ -2766,31 +3054,34 @@
         <v>135</v>
       </c>
       <c r="E7" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F7" s="8">
+      <c r="G7" s="8">
         <v>10102</v>
-      </c>
-      <c r="G7" s="10">
-        <v>1</v>
       </c>
       <c r="H7" s="10">
         <v>1</v>
       </c>
       <c r="I7" s="10">
+        <v>1</v>
+      </c>
+      <c r="J7" s="10">
         <v>39600</v>
       </c>
-      <c r="J7" s="11">
+      <c r="K7" s="11">
         <v>1500000</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="L7" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="M7" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="8" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C8" s="8">
         <v>10102</v>
       </c>
@@ -2798,32 +3089,35 @@
         <v>136</v>
       </c>
       <c r="E8" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F8" s="8">
+      <c r="G8" s="8">
         <v>10103</v>
-      </c>
-      <c r="G8" s="10">
-        <v>2</v>
       </c>
       <c r="H8" s="10">
         <v>2</v>
       </c>
       <c r="I8" s="10">
+        <v>2</v>
+      </c>
+      <c r="J8" s="10">
         <v>50400</v>
       </c>
-      <c r="J8" s="11">
+      <c r="K8" s="11">
         <v>2000000</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="L8" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="M8" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="IC8"/>
-    </row>
-    <row r="9" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID8"/>
+    </row>
+    <row r="9" spans="3:238" ht="19.5" customHeight="1">
       <c r="C9" s="8">
         <v>10103</v>
       </c>
@@ -2831,32 +3125,35 @@
         <v>137</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F9" s="8">
+      <c r="G9" s="8">
         <v>10104</v>
-      </c>
-      <c r="G9" s="10">
-        <v>3</v>
       </c>
       <c r="H9" s="10">
         <v>3</v>
       </c>
       <c r="I9" s="10">
+        <v>3</v>
+      </c>
+      <c r="J9" s="10">
         <v>61200</v>
       </c>
-      <c r="J9" s="11">
+      <c r="K9" s="11">
         <v>2500000</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="L9" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="L9" s="10" t="s">
+      <c r="M9" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="IC9"/>
-    </row>
-    <row r="10" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID9"/>
+    </row>
+    <row r="10" spans="3:238" ht="19.5" customHeight="1">
       <c r="C10" s="8">
         <v>10104</v>
       </c>
@@ -2864,32 +3161,35 @@
         <v>138</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F10" s="8">
+      <c r="G10" s="8">
         <v>10105</v>
-      </c>
-      <c r="G10" s="10">
-        <v>4</v>
       </c>
       <c r="H10" s="10">
         <v>4</v>
       </c>
       <c r="I10" s="10">
+        <v>4</v>
+      </c>
+      <c r="J10" s="10">
         <v>72000</v>
       </c>
-      <c r="J10" s="11">
+      <c r="K10" s="11">
         <v>3000000</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="L10" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="M10" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="IC10"/>
-    </row>
-    <row r="11" spans="3:237" ht="20.100000000000001" customHeight="1">
+      <c r="ID10"/>
+    </row>
+    <row r="11" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C11" s="8">
         <v>10105</v>
       </c>
@@ -2897,31 +3197,34 @@
         <v>139</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F11" s="8">
+      <c r="G11" s="8">
         <v>10106</v>
-      </c>
-      <c r="G11" s="10">
-        <v>5</v>
       </c>
       <c r="H11" s="10">
         <v>5</v>
       </c>
       <c r="I11" s="10">
+        <v>5</v>
+      </c>
+      <c r="J11" s="10">
         <v>82800</v>
       </c>
-      <c r="J11" s="11">
+      <c r="K11" s="11">
         <v>4000000</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="L11" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="M11" s="10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="12" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C12" s="8">
         <v>10106</v>
       </c>
@@ -2929,32 +3232,35 @@
         <v>140</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F12" s="8">
+      <c r="G12" s="8">
         <v>10107</v>
-      </c>
-      <c r="G12" s="10">
-        <v>6</v>
       </c>
       <c r="H12" s="10">
         <v>6</v>
       </c>
       <c r="I12" s="10">
+        <v>6</v>
+      </c>
+      <c r="J12" s="10">
         <v>93600</v>
       </c>
-      <c r="J12" s="11">
+      <c r="K12" s="11">
         <v>5000000</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="L12" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="M12" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="IC12"/>
-    </row>
-    <row r="13" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID12"/>
+    </row>
+    <row r="13" spans="3:238" ht="19.5" customHeight="1">
       <c r="C13" s="8">
         <v>10107</v>
       </c>
@@ -2962,32 +3268,35 @@
         <v>141</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F13" s="8">
+      <c r="G13" s="8">
         <v>10108</v>
-      </c>
-      <c r="G13" s="10">
-        <v>7</v>
       </c>
       <c r="H13" s="10">
         <v>7</v>
       </c>
       <c r="I13" s="10">
+        <v>7</v>
+      </c>
+      <c r="J13" s="10">
         <v>104400</v>
       </c>
-      <c r="J13" s="11">
+      <c r="K13" s="11">
         <v>6000000</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="L13" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="L13" s="10" t="s">
+      <c r="M13" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="IC13"/>
-    </row>
-    <row r="14" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID13"/>
+    </row>
+    <row r="14" spans="3:238" ht="19.5" customHeight="1">
       <c r="C14" s="8">
         <v>10108</v>
       </c>
@@ -2995,32 +3304,35 @@
         <v>142</v>
       </c>
       <c r="E14" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F14" s="8">
+      <c r="G14" s="8">
         <v>10109</v>
-      </c>
-      <c r="G14" s="10">
-        <v>8</v>
       </c>
       <c r="H14" s="10">
         <v>8</v>
       </c>
       <c r="I14" s="10">
+        <v>8</v>
+      </c>
+      <c r="J14" s="10">
         <v>115200</v>
       </c>
-      <c r="J14" s="11">
+      <c r="K14" s="11">
         <v>7000000</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="L14" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="L14" s="10" t="s">
+      <c r="M14" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="IC14"/>
-    </row>
-    <row r="15" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID14"/>
+    </row>
+    <row r="15" spans="3:238" ht="19.5" customHeight="1">
       <c r="C15" s="8">
         <v>10109</v>
       </c>
@@ -3028,32 +3340,35 @@
         <v>143</v>
       </c>
       <c r="E15" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F15" s="8">
+      <c r="G15" s="8">
         <v>10110</v>
-      </c>
-      <c r="G15" s="10">
-        <v>9</v>
       </c>
       <c r="H15" s="10">
         <v>9</v>
       </c>
       <c r="I15" s="10">
+        <v>9</v>
+      </c>
+      <c r="J15" s="10">
         <v>126000</v>
       </c>
-      <c r="J15" s="11">
+      <c r="K15" s="11">
         <v>8000000</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="L15" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="L15" s="10" t="s">
+      <c r="M15" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="IC15"/>
-    </row>
-    <row r="16" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID15"/>
+    </row>
+    <row r="16" spans="3:238" ht="19.5" customHeight="1">
       <c r="C16" s="8">
         <v>10110</v>
       </c>
@@ -3061,32 +3376,35 @@
         <v>144</v>
       </c>
       <c r="E16" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F16" s="8">
+      <c r="G16" s="8">
         <v>0</v>
-      </c>
-      <c r="G16" s="10">
-        <v>10</v>
       </c>
       <c r="H16" s="10">
         <v>10</v>
       </c>
       <c r="I16" s="10">
+        <v>10</v>
+      </c>
+      <c r="J16" s="10">
         <v>126000</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="K16" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="L16" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="L16" s="10" t="s">
+      <c r="M16" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="IC16"/>
-    </row>
-    <row r="17" spans="3:237" ht="22.5" customHeight="1">
+      <c r="ID16"/>
+    </row>
+    <row r="17" spans="3:238" ht="22.5" customHeight="1">
       <c r="C17" s="8">
         <v>10200</v>
       </c>
@@ -3094,29 +3412,32 @@
         <v>101</v>
       </c>
       <c r="E17" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="F17" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F17" s="8">
+      <c r="G17" s="8">
         <v>10201</v>
       </c>
-      <c r="G17" s="10">
+      <c r="H17" s="10">
         <v>0</v>
       </c>
-      <c r="H17" s="10">
+      <c r="I17" s="10">
         <v>1</v>
       </c>
-      <c r="I17" s="10">
+      <c r="J17" s="10">
         <v>28800</v>
       </c>
-      <c r="J17" s="11">
+      <c r="K17" s="11">
         <v>1000000</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="L17" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="L17" s="10"/>
-    </row>
-    <row r="18" spans="3:237" ht="20.100000000000001" customHeight="1">
+      <c r="M17" s="10"/>
+    </row>
+    <row r="18" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C18" s="8">
         <v>10201</v>
       </c>
@@ -3124,31 +3445,34 @@
         <v>102</v>
       </c>
       <c r="E18" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F18" s="8">
+      <c r="G18" s="8">
         <v>10202</v>
-      </c>
-      <c r="G18" s="10">
-        <v>1</v>
       </c>
       <c r="H18" s="10">
         <v>1</v>
       </c>
       <c r="I18" s="10">
+        <v>1</v>
+      </c>
+      <c r="J18" s="10">
         <v>39600</v>
       </c>
-      <c r="J18" s="11">
+      <c r="K18" s="11">
         <v>1500000</v>
       </c>
-      <c r="K18" s="11" t="s">
+      <c r="L18" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="L18" s="10" t="s">
+      <c r="M18" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="19" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C19" s="8">
         <v>10202</v>
       </c>
@@ -3156,32 +3480,35 @@
         <v>103</v>
       </c>
       <c r="E19" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="F19" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F19" s="8">
+      <c r="G19" s="8">
         <v>10203</v>
-      </c>
-      <c r="G19" s="10">
-        <v>2</v>
       </c>
       <c r="H19" s="10">
         <v>2</v>
       </c>
       <c r="I19" s="10">
+        <v>2</v>
+      </c>
+      <c r="J19" s="10">
         <v>50400</v>
       </c>
-      <c r="J19" s="11">
+      <c r="K19" s="11">
         <v>2000000</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="L19" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="L19" s="10" t="s">
+      <c r="M19" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="IC19"/>
-    </row>
-    <row r="20" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID19"/>
+    </row>
+    <row r="20" spans="3:238" ht="19.5" customHeight="1">
       <c r="C20" s="8">
         <v>10203</v>
       </c>
@@ -3189,32 +3516,35 @@
         <v>104</v>
       </c>
       <c r="E20" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F20" s="8">
+      <c r="G20" s="8">
         <v>10204</v>
-      </c>
-      <c r="G20" s="10">
-        <v>3</v>
       </c>
       <c r="H20" s="10">
         <v>3</v>
       </c>
       <c r="I20" s="10">
+        <v>3</v>
+      </c>
+      <c r="J20" s="10">
         <v>61200</v>
       </c>
-      <c r="J20" s="11">
+      <c r="K20" s="11">
         <v>2500000</v>
       </c>
-      <c r="K20" s="11" t="s">
+      <c r="L20" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="L20" s="10" t="s">
+      <c r="M20" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="IC20"/>
-    </row>
-    <row r="21" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID20"/>
+    </row>
+    <row r="21" spans="3:238" ht="19.5" customHeight="1">
       <c r="C21" s="8">
         <v>10204</v>
       </c>
@@ -3222,32 +3552,35 @@
         <v>105</v>
       </c>
       <c r="E21" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="F21" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F21" s="8">
+      <c r="G21" s="8">
         <v>10205</v>
-      </c>
-      <c r="G21" s="10">
-        <v>4</v>
       </c>
       <c r="H21" s="10">
         <v>4</v>
       </c>
       <c r="I21" s="10">
+        <v>4</v>
+      </c>
+      <c r="J21" s="10">
         <v>72000</v>
       </c>
-      <c r="J21" s="11">
+      <c r="K21" s="11">
         <v>3000000</v>
       </c>
-      <c r="K21" s="11" t="s">
+      <c r="L21" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="L21" s="10" t="s">
+      <c r="M21" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="IC21"/>
-    </row>
-    <row r="22" spans="3:237" ht="22.5" customHeight="1">
+      <c r="ID21"/>
+    </row>
+    <row r="22" spans="3:238" ht="22.5" customHeight="1">
       <c r="C22" s="8">
         <v>10205</v>
       </c>
@@ -3255,31 +3588,34 @@
         <v>106</v>
       </c>
       <c r="E22" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="F22" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F22" s="8">
+      <c r="G22" s="8">
         <v>10206</v>
-      </c>
-      <c r="G22" s="10">
-        <v>5</v>
       </c>
       <c r="H22" s="10">
         <v>5</v>
       </c>
       <c r="I22" s="10">
+        <v>5</v>
+      </c>
+      <c r="J22" s="10">
         <v>82800</v>
       </c>
-      <c r="J22" s="11">
+      <c r="K22" s="11">
         <v>4000000</v>
       </c>
-      <c r="K22" s="11" t="s">
+      <c r="L22" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="L22" s="10" t="s">
+      <c r="M22" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="23" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C23" s="8">
         <v>10206</v>
       </c>
@@ -3287,31 +3623,34 @@
         <v>107</v>
       </c>
       <c r="E23" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="F23" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F23" s="8">
+      <c r="G23" s="8">
         <v>10207</v>
-      </c>
-      <c r="G23" s="10">
-        <v>6</v>
       </c>
       <c r="H23" s="10">
         <v>6</v>
       </c>
       <c r="I23" s="10">
+        <v>6</v>
+      </c>
+      <c r="J23" s="10">
         <v>93600</v>
       </c>
-      <c r="J23" s="11">
+      <c r="K23" s="11">
         <v>5000000</v>
       </c>
-      <c r="K23" s="11" t="s">
+      <c r="L23" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="L23" s="10" t="s">
+      <c r="M23" s="10" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="24" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C24" s="8">
         <v>10207</v>
       </c>
@@ -3319,32 +3658,35 @@
         <v>108</v>
       </c>
       <c r="E24" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F24" s="8">
+      <c r="G24" s="8">
         <v>10208</v>
-      </c>
-      <c r="G24" s="10">
-        <v>7</v>
       </c>
       <c r="H24" s="10">
         <v>7</v>
       </c>
       <c r="I24" s="10">
+        <v>7</v>
+      </c>
+      <c r="J24" s="10">
         <v>104400</v>
       </c>
-      <c r="J24" s="11">
+      <c r="K24" s="11">
         <v>6000000</v>
       </c>
-      <c r="K24" s="11" t="s">
+      <c r="L24" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="L24" s="10" t="s">
+      <c r="M24" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="IC24"/>
-    </row>
-    <row r="25" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID24"/>
+    </row>
+    <row r="25" spans="3:238" ht="19.5" customHeight="1">
       <c r="C25" s="8">
         <v>10208</v>
       </c>
@@ -3352,32 +3694,35 @@
         <v>109</v>
       </c>
       <c r="E25" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="F25" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F25" s="8">
+      <c r="G25" s="8">
         <v>10209</v>
-      </c>
-      <c r="G25" s="10">
-        <v>8</v>
       </c>
       <c r="H25" s="10">
         <v>8</v>
       </c>
       <c r="I25" s="10">
+        <v>8</v>
+      </c>
+      <c r="J25" s="10">
         <v>115200</v>
       </c>
-      <c r="J25" s="11">
+      <c r="K25" s="11">
         <v>7000000</v>
       </c>
-      <c r="K25" s="11" t="s">
+      <c r="L25" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="L25" s="10" t="s">
+      <c r="M25" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="IC25"/>
-    </row>
-    <row r="26" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID25"/>
+    </row>
+    <row r="26" spans="3:238" ht="19.5" customHeight="1">
       <c r="C26" s="8">
         <v>10209</v>
       </c>
@@ -3385,32 +3730,35 @@
         <v>110</v>
       </c>
       <c r="E26" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="F26" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F26" s="8">
+      <c r="G26" s="8">
         <v>10210</v>
-      </c>
-      <c r="G26" s="10">
-        <v>9</v>
       </c>
       <c r="H26" s="10">
         <v>9</v>
       </c>
       <c r="I26" s="10">
+        <v>9</v>
+      </c>
+      <c r="J26" s="10">
         <v>126000</v>
       </c>
-      <c r="J26" s="11">
+      <c r="K26" s="11">
         <v>8000000</v>
       </c>
-      <c r="K26" s="11" t="s">
+      <c r="L26" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="L26" s="10" t="s">
+      <c r="M26" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="IC26"/>
-    </row>
-    <row r="27" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID26"/>
+    </row>
+    <row r="27" spans="3:238" ht="19.5" customHeight="1">
       <c r="C27" s="8">
         <v>10210</v>
       </c>
@@ -3418,32 +3766,35 @@
         <v>111</v>
       </c>
       <c r="E27" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="F27" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F27" s="8">
+      <c r="G27" s="8">
         <v>0</v>
-      </c>
-      <c r="G27" s="10">
-        <v>10</v>
       </c>
       <c r="H27" s="10">
         <v>10</v>
       </c>
       <c r="I27" s="10">
+        <v>10</v>
+      </c>
+      <c r="J27" s="10">
         <v>126000</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="L27" s="10" t="s">
+      <c r="L27" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="M27" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="IC27"/>
-    </row>
-    <row r="28" spans="3:237" ht="22.5" customHeight="1">
+      <c r="ID27"/>
+    </row>
+    <row r="28" spans="3:238" ht="22.5" customHeight="1">
       <c r="C28" s="8">
         <v>10300</v>
       </c>
@@ -3451,29 +3802,32 @@
         <v>146</v>
       </c>
       <c r="E28" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="F28" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F28" s="8">
+      <c r="G28" s="8">
         <v>10301</v>
       </c>
-      <c r="G28" s="10">
+      <c r="H28" s="10">
         <v>0</v>
       </c>
-      <c r="H28" s="10">
+      <c r="I28" s="10">
         <v>1</v>
       </c>
-      <c r="I28" s="10">
+      <c r="J28" s="10">
         <v>28800</v>
       </c>
-      <c r="J28" s="11">
+      <c r="K28" s="11">
         <v>1000000</v>
       </c>
-      <c r="K28" s="11" t="s">
+      <c r="L28" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="L28" s="10"/>
-    </row>
-    <row r="29" spans="3:237" ht="20.100000000000001" customHeight="1">
+      <c r="M28" s="10"/>
+    </row>
+    <row r="29" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C29" s="8">
         <v>10301</v>
       </c>
@@ -3481,31 +3835,34 @@
         <v>147</v>
       </c>
       <c r="E29" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="F29" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F29" s="8">
+      <c r="G29" s="8">
         <v>10302</v>
-      </c>
-      <c r="G29" s="10">
-        <v>1</v>
       </c>
       <c r="H29" s="10">
         <v>1</v>
       </c>
       <c r="I29" s="10">
+        <v>1</v>
+      </c>
+      <c r="J29" s="10">
         <v>39600</v>
       </c>
-      <c r="J29" s="11">
+      <c r="K29" s="11">
         <v>1500000</v>
       </c>
-      <c r="K29" s="11" t="s">
+      <c r="L29" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="L29" s="10" t="s">
+      <c r="M29" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="30" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C30" s="8">
         <v>10302</v>
       </c>
@@ -3513,32 +3870,35 @@
         <v>148</v>
       </c>
       <c r="E30" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="F30" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F30" s="8">
+      <c r="G30" s="8">
         <v>10303</v>
-      </c>
-      <c r="G30" s="10">
-        <v>2</v>
       </c>
       <c r="H30" s="10">
         <v>2</v>
       </c>
       <c r="I30" s="10">
+        <v>2</v>
+      </c>
+      <c r="J30" s="10">
         <v>50400</v>
       </c>
-      <c r="J30" s="11">
+      <c r="K30" s="11">
         <v>2000000</v>
       </c>
-      <c r="K30" s="11" t="s">
+      <c r="L30" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="L30" s="10" t="s">
+      <c r="M30" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="IC30"/>
-    </row>
-    <row r="31" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID30"/>
+    </row>
+    <row r="31" spans="3:238" ht="19.5" customHeight="1">
       <c r="C31" s="8">
         <v>10303</v>
       </c>
@@ -3546,32 +3906,35 @@
         <v>149</v>
       </c>
       <c r="E31" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="F31" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F31" s="8">
+      <c r="G31" s="8">
         <v>10304</v>
-      </c>
-      <c r="G31" s="10">
-        <v>3</v>
       </c>
       <c r="H31" s="10">
         <v>3</v>
       </c>
       <c r="I31" s="10">
+        <v>3</v>
+      </c>
+      <c r="J31" s="10">
         <v>61200</v>
       </c>
-      <c r="J31" s="11">
+      <c r="K31" s="11">
         <v>2500000</v>
       </c>
-      <c r="K31" s="11" t="s">
+      <c r="L31" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="L31" s="10" t="s">
+      <c r="M31" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="IC31"/>
-    </row>
-    <row r="32" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID31"/>
+    </row>
+    <row r="32" spans="3:238" ht="19.5" customHeight="1">
       <c r="C32" s="8">
         <v>10304</v>
       </c>
@@ -3579,32 +3942,35 @@
         <v>150</v>
       </c>
       <c r="E32" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="F32" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F32" s="8">
+      <c r="G32" s="8">
         <v>10305</v>
-      </c>
-      <c r="G32" s="10">
-        <v>4</v>
       </c>
       <c r="H32" s="10">
         <v>4</v>
       </c>
       <c r="I32" s="10">
+        <v>4</v>
+      </c>
+      <c r="J32" s="10">
         <v>72000</v>
       </c>
-      <c r="J32" s="11">
+      <c r="K32" s="11">
         <v>3000000</v>
       </c>
-      <c r="K32" s="11" t="s">
+      <c r="L32" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="L32" s="10" t="s">
+      <c r="M32" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="IC32"/>
-    </row>
-    <row r="33" spans="3:237" ht="20.100000000000001" customHeight="1">
+      <c r="ID32"/>
+    </row>
+    <row r="33" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C33" s="8">
         <v>10305</v>
       </c>
@@ -3612,31 +3978,34 @@
         <v>151</v>
       </c>
       <c r="E33" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="F33" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F33" s="8">
+      <c r="G33" s="8">
         <v>10306</v>
-      </c>
-      <c r="G33" s="10">
-        <v>5</v>
       </c>
       <c r="H33" s="10">
         <v>5</v>
       </c>
       <c r="I33" s="10">
+        <v>5</v>
+      </c>
+      <c r="J33" s="10">
         <v>82800</v>
       </c>
-      <c r="J33" s="11">
+      <c r="K33" s="11">
         <v>4000000</v>
       </c>
-      <c r="K33" s="11" t="s">
+      <c r="L33" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="L33" s="10" t="s">
+      <c r="M33" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="34" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C34" s="8">
         <v>10306</v>
       </c>
@@ -3644,32 +4013,35 @@
         <v>152</v>
       </c>
       <c r="E34" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="F34" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F34" s="8">
+      <c r="G34" s="8">
         <v>10307</v>
-      </c>
-      <c r="G34" s="10">
-        <v>6</v>
       </c>
       <c r="H34" s="10">
         <v>6</v>
       </c>
       <c r="I34" s="10">
+        <v>6</v>
+      </c>
+      <c r="J34" s="10">
         <v>93600</v>
       </c>
-      <c r="J34" s="11">
+      <c r="K34" s="11">
         <v>5000000</v>
       </c>
-      <c r="K34" s="11" t="s">
+      <c r="L34" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="L34" s="10" t="s">
+      <c r="M34" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="IC34"/>
-    </row>
-    <row r="35" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID34"/>
+    </row>
+    <row r="35" spans="3:238" ht="19.5" customHeight="1">
       <c r="C35" s="8">
         <v>10307</v>
       </c>
@@ -3677,32 +4049,35 @@
         <v>153</v>
       </c>
       <c r="E35" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F35" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F35" s="8">
+      <c r="G35" s="8">
         <v>10308</v>
-      </c>
-      <c r="G35" s="10">
-        <v>7</v>
       </c>
       <c r="H35" s="10">
         <v>7</v>
       </c>
       <c r="I35" s="10">
+        <v>7</v>
+      </c>
+      <c r="J35" s="10">
         <v>104400</v>
       </c>
-      <c r="J35" s="11">
+      <c r="K35" s="11">
         <v>6000000</v>
       </c>
-      <c r="K35" s="11" t="s">
+      <c r="L35" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="L35" s="10" t="s">
+      <c r="M35" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="IC35"/>
-    </row>
-    <row r="36" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID35"/>
+    </row>
+    <row r="36" spans="3:238" ht="19.5" customHeight="1">
       <c r="C36" s="8">
         <v>10308</v>
       </c>
@@ -3710,32 +4085,35 @@
         <v>154</v>
       </c>
       <c r="E36" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="F36" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F36" s="8">
+      <c r="G36" s="8">
         <v>10309</v>
-      </c>
-      <c r="G36" s="10">
-        <v>8</v>
       </c>
       <c r="H36" s="10">
         <v>8</v>
       </c>
       <c r="I36" s="10">
+        <v>8</v>
+      </c>
+      <c r="J36" s="10">
         <v>115200</v>
       </c>
-      <c r="J36" s="11">
+      <c r="K36" s="11">
         <v>7000000</v>
       </c>
-      <c r="K36" s="11" t="s">
+      <c r="L36" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="L36" s="10" t="s">
+      <c r="M36" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="IC36"/>
-    </row>
-    <row r="37" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID36"/>
+    </row>
+    <row r="37" spans="3:238" ht="19.5" customHeight="1">
       <c r="C37" s="8">
         <v>10309</v>
       </c>
@@ -3743,32 +4121,35 @@
         <v>155</v>
       </c>
       <c r="E37" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="F37" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F37" s="8">
+      <c r="G37" s="8">
         <v>10310</v>
-      </c>
-      <c r="G37" s="10">
-        <v>9</v>
       </c>
       <c r="H37" s="10">
         <v>9</v>
       </c>
       <c r="I37" s="10">
+        <v>9</v>
+      </c>
+      <c r="J37" s="10">
         <v>126000</v>
       </c>
-      <c r="J37" s="11">
+      <c r="K37" s="11">
         <v>8000000</v>
       </c>
-      <c r="K37" s="11" t="s">
+      <c r="L37" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="L37" s="10" t="s">
+      <c r="M37" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="IC37"/>
-    </row>
-    <row r="38" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID37"/>
+    </row>
+    <row r="38" spans="3:238" ht="19.5" customHeight="1">
       <c r="C38" s="8">
         <v>10310</v>
       </c>
@@ -3776,32 +4157,35 @@
         <v>156</v>
       </c>
       <c r="E38" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="F38" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F38" s="8">
+      <c r="G38" s="8">
         <v>0</v>
-      </c>
-      <c r="G38" s="10">
-        <v>10</v>
       </c>
       <c r="H38" s="10">
         <v>10</v>
       </c>
       <c r="I38" s="10">
+        <v>10</v>
+      </c>
+      <c r="J38" s="10">
         <v>126000</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="L38" s="10" t="s">
+      <c r="L38" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="M38" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="IC38"/>
-    </row>
-    <row r="39" spans="3:237" ht="22.5" customHeight="1">
+      <c r="ID38"/>
+    </row>
+    <row r="39" spans="3:238" ht="22.5" customHeight="1">
       <c r="C39" s="8">
         <v>10400</v>
       </c>
@@ -3809,29 +4193,32 @@
         <v>167</v>
       </c>
       <c r="E39" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="F39" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F39" s="8">
+      <c r="G39" s="8">
         <v>10401</v>
       </c>
-      <c r="G39" s="10">
+      <c r="H39" s="10">
         <v>0</v>
       </c>
-      <c r="H39" s="10">
+      <c r="I39" s="10">
         <v>1</v>
       </c>
-      <c r="I39" s="10">
+      <c r="J39" s="10">
         <v>28800</v>
       </c>
-      <c r="J39" s="11">
+      <c r="K39" s="11">
         <v>1000000</v>
       </c>
-      <c r="K39" s="11" t="s">
+      <c r="L39" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="L39" s="10"/>
-    </row>
-    <row r="40" spans="3:237" ht="20.100000000000001" customHeight="1">
+      <c r="M39" s="10"/>
+    </row>
+    <row r="40" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C40" s="8">
         <v>10401</v>
       </c>
@@ -3839,31 +4226,34 @@
         <v>168</v>
       </c>
       <c r="E40" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F40" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F40" s="8">
+      <c r="G40" s="8">
         <v>10402</v>
-      </c>
-      <c r="G40" s="10">
-        <v>1</v>
       </c>
       <c r="H40" s="10">
         <v>1</v>
       </c>
       <c r="I40" s="10">
+        <v>1</v>
+      </c>
+      <c r="J40" s="10">
         <v>39600</v>
       </c>
-      <c r="J40" s="11">
+      <c r="K40" s="11">
         <v>1500000</v>
       </c>
-      <c r="K40" s="11" t="s">
+      <c r="L40" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="L40" s="10" t="s">
+      <c r="M40" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="41" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C41" s="8">
         <v>10402</v>
       </c>
@@ -3871,32 +4261,35 @@
         <v>169</v>
       </c>
       <c r="E41" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="F41" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F41" s="8">
+      <c r="G41" s="8">
         <v>10403</v>
-      </c>
-      <c r="G41" s="10">
-        <v>2</v>
       </c>
       <c r="H41" s="10">
         <v>2</v>
       </c>
       <c r="I41" s="10">
+        <v>2</v>
+      </c>
+      <c r="J41" s="10">
         <v>50400</v>
       </c>
-      <c r="J41" s="11">
+      <c r="K41" s="11">
         <v>2000000</v>
       </c>
-      <c r="K41" s="11" t="s">
+      <c r="L41" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="L41" s="10" t="s">
+      <c r="M41" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="IC41"/>
-    </row>
-    <row r="42" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID41"/>
+    </row>
+    <row r="42" spans="3:238" ht="19.5" customHeight="1">
       <c r="C42" s="8">
         <v>10403</v>
       </c>
@@ -3904,32 +4297,35 @@
         <v>170</v>
       </c>
       <c r="E42" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F42" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F42" s="8">
+      <c r="G42" s="8">
         <v>10404</v>
-      </c>
-      <c r="G42" s="10">
-        <v>3</v>
       </c>
       <c r="H42" s="10">
         <v>3</v>
       </c>
       <c r="I42" s="10">
+        <v>3</v>
+      </c>
+      <c r="J42" s="10">
         <v>61200</v>
       </c>
-      <c r="J42" s="11">
+      <c r="K42" s="11">
         <v>2500000</v>
       </c>
-      <c r="K42" s="11" t="s">
+      <c r="L42" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="L42" s="10" t="s">
+      <c r="M42" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="IC42"/>
-    </row>
-    <row r="43" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID42"/>
+    </row>
+    <row r="43" spans="3:238" ht="19.5" customHeight="1">
       <c r="C43" s="8">
         <v>10404</v>
       </c>
@@ -3937,32 +4333,35 @@
         <v>171</v>
       </c>
       <c r="E43" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="F43" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F43" s="8">
+      <c r="G43" s="8">
         <v>10405</v>
-      </c>
-      <c r="G43" s="10">
-        <v>4</v>
       </c>
       <c r="H43" s="10">
         <v>4</v>
       </c>
       <c r="I43" s="10">
+        <v>4</v>
+      </c>
+      <c r="J43" s="10">
         <v>72000</v>
       </c>
-      <c r="J43" s="11">
+      <c r="K43" s="11">
         <v>3000000</v>
       </c>
-      <c r="K43" s="11" t="s">
+      <c r="L43" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="L43" s="10" t="s">
+      <c r="M43" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="IC43"/>
-    </row>
-    <row r="44" spans="3:237" ht="22.5" customHeight="1">
+      <c r="ID43"/>
+    </row>
+    <row r="44" spans="3:238" ht="22.5" customHeight="1">
       <c r="C44" s="8">
         <v>10405</v>
       </c>
@@ -3970,31 +4369,34 @@
         <v>172</v>
       </c>
       <c r="E44" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="F44" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F44" s="8">
+      <c r="G44" s="8">
         <v>10406</v>
-      </c>
-      <c r="G44" s="10">
-        <v>5</v>
       </c>
       <c r="H44" s="10">
         <v>5</v>
       </c>
       <c r="I44" s="10">
+        <v>5</v>
+      </c>
+      <c r="J44" s="10">
         <v>82800</v>
       </c>
-      <c r="J44" s="11">
+      <c r="K44" s="11">
         <v>4000000</v>
       </c>
-      <c r="K44" s="11" t="s">
+      <c r="L44" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="L44" s="10" t="s">
+      <c r="M44" s="10" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="45" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="45" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C45" s="8">
         <v>10406</v>
       </c>
@@ -4002,31 +4404,34 @@
         <v>173</v>
       </c>
       <c r="E45" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F45" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F45" s="8">
+      <c r="G45" s="8">
         <v>10407</v>
-      </c>
-      <c r="G45" s="10">
-        <v>6</v>
       </c>
       <c r="H45" s="10">
         <v>6</v>
       </c>
       <c r="I45" s="10">
+        <v>6</v>
+      </c>
+      <c r="J45" s="10">
         <v>93600</v>
       </c>
-      <c r="J45" s="11">
+      <c r="K45" s="11">
         <v>5000000</v>
       </c>
-      <c r="K45" s="11" t="s">
+      <c r="L45" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="L45" s="10" t="s">
+      <c r="M45" s="10" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="46" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="46" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C46" s="8">
         <v>10407</v>
       </c>
@@ -4034,32 +4439,35 @@
         <v>174</v>
       </c>
       <c r="E46" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="F46" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F46" s="8">
+      <c r="G46" s="8">
         <v>10408</v>
-      </c>
-      <c r="G46" s="10">
-        <v>7</v>
       </c>
       <c r="H46" s="10">
         <v>7</v>
       </c>
       <c r="I46" s="10">
+        <v>7</v>
+      </c>
+      <c r="J46" s="10">
         <v>104400</v>
       </c>
-      <c r="J46" s="11">
+      <c r="K46" s="11">
         <v>6000000</v>
       </c>
-      <c r="K46" s="11" t="s">
+      <c r="L46" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="L46" s="10" t="s">
+      <c r="M46" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="IC46"/>
-    </row>
-    <row r="47" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID46"/>
+    </row>
+    <row r="47" spans="3:238" ht="19.5" customHeight="1">
       <c r="C47" s="8">
         <v>10408</v>
       </c>
@@ -4067,32 +4475,35 @@
         <v>175</v>
       </c>
       <c r="E47" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="F47" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F47" s="8">
+      <c r="G47" s="8">
         <v>10409</v>
-      </c>
-      <c r="G47" s="10">
-        <v>8</v>
       </c>
       <c r="H47" s="10">
         <v>8</v>
       </c>
       <c r="I47" s="10">
+        <v>8</v>
+      </c>
+      <c r="J47" s="10">
         <v>115200</v>
       </c>
-      <c r="J47" s="11">
+      <c r="K47" s="11">
         <v>7000000</v>
       </c>
-      <c r="K47" s="11" t="s">
+      <c r="L47" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="L47" s="10" t="s">
+      <c r="M47" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="IC47"/>
-    </row>
-    <row r="48" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID47"/>
+    </row>
+    <row r="48" spans="3:238" ht="19.5" customHeight="1">
       <c r="C48" s="8">
         <v>10409</v>
       </c>
@@ -4100,32 +4511,35 @@
         <v>176</v>
       </c>
       <c r="E48" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="F48" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F48" s="8">
+      <c r="G48" s="8">
         <v>10410</v>
-      </c>
-      <c r="G48" s="10">
-        <v>9</v>
       </c>
       <c r="H48" s="10">
         <v>9</v>
       </c>
       <c r="I48" s="10">
+        <v>9</v>
+      </c>
+      <c r="J48" s="10">
         <v>126000</v>
       </c>
-      <c r="J48" s="11">
+      <c r="K48" s="11">
         <v>8000000</v>
       </c>
-      <c r="K48" s="11" t="s">
+      <c r="L48" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="L48" s="10" t="s">
+      <c r="M48" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="IC48"/>
-    </row>
-    <row r="49" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID48"/>
+    </row>
+    <row r="49" spans="3:238" ht="19.5" customHeight="1">
       <c r="C49" s="8">
         <v>10410</v>
       </c>
@@ -4133,32 +4547,35 @@
         <v>177</v>
       </c>
       <c r="E49" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="F49" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F49" s="8">
+      <c r="G49" s="8">
         <v>0</v>
-      </c>
-      <c r="G49" s="10">
-        <v>10</v>
       </c>
       <c r="H49" s="10">
         <v>10</v>
       </c>
       <c r="I49" s="10">
+        <v>10</v>
+      </c>
+      <c r="J49" s="10">
         <v>126000</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="L49" s="10" t="s">
+      <c r="L49" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="M49" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="IC49"/>
-    </row>
-    <row r="50" spans="3:237" ht="22.5" customHeight="1">
+      <c r="ID49"/>
+    </row>
+    <row r="50" spans="3:238" ht="22.5" customHeight="1">
       <c r="C50" s="8">
         <v>10500</v>
       </c>
@@ -4166,29 +4583,32 @@
         <v>157</v>
       </c>
       <c r="E50" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="F50" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F50" s="8">
+      <c r="G50" s="8">
         <v>10501</v>
       </c>
-      <c r="G50" s="10">
+      <c r="H50" s="10">
         <v>0</v>
       </c>
-      <c r="H50" s="10">
+      <c r="I50" s="10">
         <v>1</v>
       </c>
-      <c r="I50" s="10">
+      <c r="J50" s="10">
         <v>28800</v>
       </c>
-      <c r="J50" s="11">
+      <c r="K50" s="11">
         <v>1000000</v>
       </c>
-      <c r="K50" s="11" t="s">
+      <c r="L50" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="L50" s="10"/>
-    </row>
-    <row r="51" spans="3:237" ht="20.100000000000001" customHeight="1">
+      <c r="M50" s="10"/>
+    </row>
+    <row r="51" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C51" s="8">
         <v>10501</v>
       </c>
@@ -4196,31 +4616,34 @@
         <v>158</v>
       </c>
       <c r="E51" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="F51" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F51" s="8">
+      <c r="G51" s="8">
         <v>10502</v>
-      </c>
-      <c r="G51" s="10">
-        <v>1</v>
       </c>
       <c r="H51" s="10">
         <v>1</v>
       </c>
       <c r="I51" s="10">
+        <v>1</v>
+      </c>
+      <c r="J51" s="10">
         <v>39600</v>
       </c>
-      <c r="J51" s="11">
+      <c r="K51" s="11">
         <v>1500000</v>
       </c>
-      <c r="K51" s="11" t="s">
+      <c r="L51" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="L51" s="10" t="s">
+      <c r="M51" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="52" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C52" s="8">
         <v>10502</v>
       </c>
@@ -4228,32 +4651,35 @@
         <v>145</v>
       </c>
       <c r="E52" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="F52" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F52" s="8">
+      <c r="G52" s="8">
         <v>10503</v>
-      </c>
-      <c r="G52" s="10">
-        <v>2</v>
       </c>
       <c r="H52" s="10">
         <v>2</v>
       </c>
       <c r="I52" s="10">
+        <v>2</v>
+      </c>
+      <c r="J52" s="10">
         <v>50400</v>
       </c>
-      <c r="J52" s="11">
+      <c r="K52" s="11">
         <v>2000000</v>
       </c>
-      <c r="K52" s="11" t="s">
+      <c r="L52" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="L52" s="10" t="s">
+      <c r="M52" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="IC52"/>
-    </row>
-    <row r="53" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID52"/>
+    </row>
+    <row r="53" spans="3:238" ht="19.5" customHeight="1">
       <c r="C53" s="8">
         <v>10503</v>
       </c>
@@ -4261,32 +4687,35 @@
         <v>159</v>
       </c>
       <c r="E53" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="F53" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F53" s="8">
+      <c r="G53" s="8">
         <v>10504</v>
-      </c>
-      <c r="G53" s="10">
-        <v>3</v>
       </c>
       <c r="H53" s="10">
         <v>3</v>
       </c>
       <c r="I53" s="10">
+        <v>3</v>
+      </c>
+      <c r="J53" s="10">
         <v>61200</v>
       </c>
-      <c r="J53" s="11">
+      <c r="K53" s="11">
         <v>2500000</v>
       </c>
-      <c r="K53" s="11" t="s">
+      <c r="L53" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="L53" s="10" t="s">
+      <c r="M53" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="IC53"/>
-    </row>
-    <row r="54" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID53"/>
+    </row>
+    <row r="54" spans="3:238" ht="19.5" customHeight="1">
       <c r="C54" s="8">
         <v>10504</v>
       </c>
@@ -4294,32 +4723,35 @@
         <v>160</v>
       </c>
       <c r="E54" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="F54" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F54" s="8">
+      <c r="G54" s="8">
         <v>10505</v>
-      </c>
-      <c r="G54" s="10">
-        <v>4</v>
       </c>
       <c r="H54" s="10">
         <v>4</v>
       </c>
       <c r="I54" s="10">
+        <v>4</v>
+      </c>
+      <c r="J54" s="10">
         <v>72000</v>
       </c>
-      <c r="J54" s="11">
+      <c r="K54" s="11">
         <v>3000000</v>
       </c>
-      <c r="K54" s="11" t="s">
+      <c r="L54" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="L54" s="10" t="s">
+      <c r="M54" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="IC54"/>
-    </row>
-    <row r="55" spans="3:237" ht="22.5" customHeight="1">
+      <c r="ID54"/>
+    </row>
+    <row r="55" spans="3:238" ht="22.5" customHeight="1">
       <c r="C55" s="8">
         <v>10505</v>
       </c>
@@ -4327,31 +4759,34 @@
         <v>161</v>
       </c>
       <c r="E55" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="F55" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F55" s="8">
+      <c r="G55" s="8">
         <v>10506</v>
-      </c>
-      <c r="G55" s="10">
-        <v>5</v>
       </c>
       <c r="H55" s="10">
         <v>5</v>
       </c>
       <c r="I55" s="10">
+        <v>5</v>
+      </c>
+      <c r="J55" s="10">
         <v>82800</v>
       </c>
-      <c r="J55" s="11">
+      <c r="K55" s="11">
         <v>4000000</v>
       </c>
-      <c r="K55" s="11" t="s">
+      <c r="L55" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="L55" s="10" t="s">
+      <c r="M55" s="10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="56" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C56" s="8">
         <v>10506</v>
       </c>
@@ -4359,31 +4794,34 @@
         <v>162</v>
       </c>
       <c r="E56" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="F56" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F56" s="8">
+      <c r="G56" s="8">
         <v>10507</v>
-      </c>
-      <c r="G56" s="10">
-        <v>6</v>
       </c>
       <c r="H56" s="10">
         <v>6</v>
       </c>
       <c r="I56" s="10">
+        <v>6</v>
+      </c>
+      <c r="J56" s="10">
         <v>93600</v>
       </c>
-      <c r="J56" s="11">
+      <c r="K56" s="11">
         <v>5000000</v>
       </c>
-      <c r="K56" s="11" t="s">
+      <c r="L56" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="L56" s="10" t="s">
+      <c r="M56" s="10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="57" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C57" s="8">
         <v>10507</v>
       </c>
@@ -4391,32 +4829,35 @@
         <v>163</v>
       </c>
       <c r="E57" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="F57" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F57" s="8">
+      <c r="G57" s="8">
         <v>10508</v>
-      </c>
-      <c r="G57" s="10">
-        <v>7</v>
       </c>
       <c r="H57" s="10">
         <v>7</v>
       </c>
       <c r="I57" s="10">
+        <v>7</v>
+      </c>
+      <c r="J57" s="10">
         <v>104400</v>
       </c>
-      <c r="J57" s="11">
+      <c r="K57" s="11">
         <v>6000000</v>
       </c>
-      <c r="K57" s="11" t="s">
+      <c r="L57" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="L57" s="10" t="s">
+      <c r="M57" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="IC57"/>
-    </row>
-    <row r="58" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID57"/>
+    </row>
+    <row r="58" spans="3:238" ht="19.5" customHeight="1">
       <c r="C58" s="8">
         <v>10508</v>
       </c>
@@ -4424,32 +4865,35 @@
         <v>164</v>
       </c>
       <c r="E58" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="F58" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F58" s="8">
+      <c r="G58" s="8">
         <v>10509</v>
-      </c>
-      <c r="G58" s="10">
-        <v>8</v>
       </c>
       <c r="H58" s="10">
         <v>8</v>
       </c>
       <c r="I58" s="10">
+        <v>8</v>
+      </c>
+      <c r="J58" s="10">
         <v>115200</v>
       </c>
-      <c r="J58" s="11">
+      <c r="K58" s="11">
         <v>7000000</v>
       </c>
-      <c r="K58" s="11" t="s">
+      <c r="L58" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="L58" s="10" t="s">
+      <c r="M58" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="IC58"/>
-    </row>
-    <row r="59" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID58"/>
+    </row>
+    <row r="59" spans="3:238" ht="19.5" customHeight="1">
       <c r="C59" s="8">
         <v>10509</v>
       </c>
@@ -4457,32 +4901,35 @@
         <v>165</v>
       </c>
       <c r="E59" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="F59" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F59" s="8">
+      <c r="G59" s="8">
         <v>10510</v>
-      </c>
-      <c r="G59" s="10">
-        <v>9</v>
       </c>
       <c r="H59" s="10">
         <v>9</v>
       </c>
       <c r="I59" s="10">
+        <v>9</v>
+      </c>
+      <c r="J59" s="10">
         <v>126000</v>
       </c>
-      <c r="J59" s="11">
+      <c r="K59" s="11">
         <v>8000000</v>
       </c>
-      <c r="K59" s="11" t="s">
+      <c r="L59" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="L59" s="10" t="s">
+      <c r="M59" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="IC59"/>
-    </row>
-    <row r="60" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID59"/>
+    </row>
+    <row r="60" spans="3:238" ht="19.5" customHeight="1">
       <c r="C60" s="8">
         <v>10510</v>
       </c>
@@ -4490,32 +4937,35 @@
         <v>166</v>
       </c>
       <c r="E60" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="F60" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F60" s="8">
+      <c r="G60" s="8">
         <v>0</v>
-      </c>
-      <c r="G60" s="10">
-        <v>10</v>
       </c>
       <c r="H60" s="10">
         <v>10</v>
       </c>
       <c r="I60" s="10">
+        <v>10</v>
+      </c>
+      <c r="J60" s="10">
         <v>126000</v>
-      </c>
-      <c r="J60" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="L60" s="10" t="s">
+      <c r="L60" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="M60" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="IC60"/>
-    </row>
-    <row r="61" spans="3:237" ht="22.5" customHeight="1">
+      <c r="ID60"/>
+    </row>
+    <row r="61" spans="3:238" ht="22.5" customHeight="1">
       <c r="C61" s="8">
         <v>10600</v>
       </c>
@@ -4523,29 +4973,32 @@
         <v>178</v>
       </c>
       <c r="E61" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="F61" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F61" s="8">
+      <c r="G61" s="8">
         <v>10601</v>
       </c>
-      <c r="G61" s="10">
+      <c r="H61" s="10">
         <v>0</v>
       </c>
-      <c r="H61" s="10">
+      <c r="I61" s="10">
         <v>1</v>
       </c>
-      <c r="I61" s="10">
+      <c r="J61" s="10">
         <v>28800</v>
       </c>
-      <c r="J61" s="11">
+      <c r="K61" s="11">
         <v>1000000</v>
       </c>
-      <c r="K61" s="11" t="s">
+      <c r="L61" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="L61" s="10"/>
-    </row>
-    <row r="62" spans="3:237" ht="20.100000000000001" customHeight="1">
+      <c r="M61" s="10"/>
+    </row>
+    <row r="62" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C62" s="8">
         <v>10601</v>
       </c>
@@ -4553,31 +5006,34 @@
         <v>179</v>
       </c>
       <c r="E62" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="F62" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F62" s="8">
+      <c r="G62" s="8">
         <v>10602</v>
-      </c>
-      <c r="G62" s="10">
-        <v>1</v>
       </c>
       <c r="H62" s="10">
         <v>1</v>
       </c>
       <c r="I62" s="10">
+        <v>1</v>
+      </c>
+      <c r="J62" s="10">
         <v>39600</v>
       </c>
-      <c r="J62" s="11">
+      <c r="K62" s="11">
         <v>1500000</v>
       </c>
-      <c r="K62" s="11" t="s">
+      <c r="L62" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="L62" s="10" t="s">
+      <c r="M62" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="63" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C63" s="8">
         <v>10602</v>
       </c>
@@ -4585,32 +5041,35 @@
         <v>180</v>
       </c>
       <c r="E63" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="F63" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F63" s="8">
+      <c r="G63" s="8">
         <v>10603</v>
-      </c>
-      <c r="G63" s="10">
-        <v>2</v>
       </c>
       <c r="H63" s="10">
         <v>2</v>
       </c>
       <c r="I63" s="10">
+        <v>2</v>
+      </c>
+      <c r="J63" s="10">
         <v>50400</v>
       </c>
-      <c r="J63" s="11">
+      <c r="K63" s="11">
         <v>2000000</v>
       </c>
-      <c r="K63" s="11" t="s">
+      <c r="L63" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="L63" s="10" t="s">
+      <c r="M63" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="IC63"/>
-    </row>
-    <row r="64" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID63"/>
+    </row>
+    <row r="64" spans="3:238" ht="19.5" customHeight="1">
       <c r="C64" s="8">
         <v>10603</v>
       </c>
@@ -4618,32 +5077,35 @@
         <v>181</v>
       </c>
       <c r="E64" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="F64" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F64" s="8">
+      <c r="G64" s="8">
         <v>10604</v>
-      </c>
-      <c r="G64" s="10">
-        <v>3</v>
       </c>
       <c r="H64" s="10">
         <v>3</v>
       </c>
       <c r="I64" s="10">
+        <v>3</v>
+      </c>
+      <c r="J64" s="10">
         <v>61200</v>
       </c>
-      <c r="J64" s="11">
+      <c r="K64" s="11">
         <v>2500000</v>
       </c>
-      <c r="K64" s="11" t="s">
+      <c r="L64" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="L64" s="10" t="s">
+      <c r="M64" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="IC64"/>
-    </row>
-    <row r="65" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID64"/>
+    </row>
+    <row r="65" spans="3:238" ht="19.5" customHeight="1">
       <c r="C65" s="8">
         <v>10604</v>
       </c>
@@ -4651,32 +5113,35 @@
         <v>182</v>
       </c>
       <c r="E65" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="F65" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F65" s="8">
+      <c r="G65" s="8">
         <v>10605</v>
-      </c>
-      <c r="G65" s="10">
-        <v>4</v>
       </c>
       <c r="H65" s="10">
         <v>4</v>
       </c>
       <c r="I65" s="10">
+        <v>4</v>
+      </c>
+      <c r="J65" s="10">
         <v>72000</v>
       </c>
-      <c r="J65" s="11">
+      <c r="K65" s="11">
         <v>3000000</v>
       </c>
-      <c r="K65" s="11" t="s">
+      <c r="L65" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="L65" s="10" t="s">
+      <c r="M65" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="IC65"/>
-    </row>
-    <row r="66" spans="3:237" ht="22.5" customHeight="1">
+      <c r="ID65"/>
+    </row>
+    <row r="66" spans="3:238" ht="22.5" customHeight="1">
       <c r="C66" s="8">
         <v>10605</v>
       </c>
@@ -4684,31 +5149,34 @@
         <v>183</v>
       </c>
       <c r="E66" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="F66" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F66" s="8">
+      <c r="G66" s="8">
         <v>10606</v>
-      </c>
-      <c r="G66" s="10">
-        <v>5</v>
       </c>
       <c r="H66" s="10">
         <v>5</v>
       </c>
       <c r="I66" s="10">
+        <v>5</v>
+      </c>
+      <c r="J66" s="10">
         <v>82800</v>
       </c>
-      <c r="J66" s="11">
+      <c r="K66" s="11">
         <v>4000000</v>
       </c>
-      <c r="K66" s="11" t="s">
+      <c r="L66" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="L66" s="10" t="s">
+      <c r="M66" s="10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="67" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="67" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C67" s="8">
         <v>10606</v>
       </c>
@@ -4716,31 +5184,34 @@
         <v>184</v>
       </c>
       <c r="E67" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="F67" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F67" s="8">
+      <c r="G67" s="8">
         <v>10607</v>
-      </c>
-      <c r="G67" s="10">
-        <v>6</v>
       </c>
       <c r="H67" s="10">
         <v>6</v>
       </c>
       <c r="I67" s="10">
+        <v>6</v>
+      </c>
+      <c r="J67" s="10">
         <v>93600</v>
       </c>
-      <c r="J67" s="11">
+      <c r="K67" s="11">
         <v>5000000</v>
       </c>
-      <c r="K67" s="11" t="s">
+      <c r="L67" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="L67" s="10" t="s">
+      <c r="M67" s="10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="68" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="68" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C68" s="8">
         <v>10607</v>
       </c>
@@ -4748,32 +5219,35 @@
         <v>185</v>
       </c>
       <c r="E68" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="F68" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F68" s="8">
+      <c r="G68" s="8">
         <v>10608</v>
-      </c>
-      <c r="G68" s="10">
-        <v>7</v>
       </c>
       <c r="H68" s="10">
         <v>7</v>
       </c>
       <c r="I68" s="10">
+        <v>7</v>
+      </c>
+      <c r="J68" s="10">
         <v>104400</v>
       </c>
-      <c r="J68" s="11">
+      <c r="K68" s="11">
         <v>6000000</v>
       </c>
-      <c r="K68" s="11" t="s">
+      <c r="L68" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="L68" s="10" t="s">
+      <c r="M68" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="IC68"/>
-    </row>
-    <row r="69" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID68"/>
+    </row>
+    <row r="69" spans="3:238" ht="19.5" customHeight="1">
       <c r="C69" s="8">
         <v>10608</v>
       </c>
@@ -4781,32 +5255,35 @@
         <v>186</v>
       </c>
       <c r="E69" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="F69" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F69" s="8">
+      <c r="G69" s="8">
         <v>10609</v>
-      </c>
-      <c r="G69" s="10">
-        <v>8</v>
       </c>
       <c r="H69" s="10">
         <v>8</v>
       </c>
       <c r="I69" s="10">
+        <v>8</v>
+      </c>
+      <c r="J69" s="10">
         <v>115200</v>
       </c>
-      <c r="J69" s="11">
+      <c r="K69" s="11">
         <v>7000000</v>
       </c>
-      <c r="K69" s="11" t="s">
+      <c r="L69" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="L69" s="10" t="s">
+      <c r="M69" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="IC69"/>
-    </row>
-    <row r="70" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID69"/>
+    </row>
+    <row r="70" spans="3:238" ht="19.5" customHeight="1">
       <c r="C70" s="8">
         <v>10609</v>
       </c>
@@ -4814,32 +5291,35 @@
         <v>187</v>
       </c>
       <c r="E70" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="F70" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F70" s="8">
+      <c r="G70" s="8">
         <v>10610</v>
-      </c>
-      <c r="G70" s="10">
-        <v>9</v>
       </c>
       <c r="H70" s="10">
         <v>9</v>
       </c>
       <c r="I70" s="10">
+        <v>9</v>
+      </c>
+      <c r="J70" s="10">
         <v>126000</v>
       </c>
-      <c r="J70" s="11">
+      <c r="K70" s="11">
         <v>8000000</v>
       </c>
-      <c r="K70" s="11" t="s">
+      <c r="L70" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="L70" s="10" t="s">
+      <c r="M70" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="IC70"/>
-    </row>
-    <row r="71" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID70"/>
+    </row>
+    <row r="71" spans="3:238" ht="19.5" customHeight="1">
       <c r="C71" s="8">
         <v>10610</v>
       </c>
@@ -4847,32 +5327,35 @@
         <v>188</v>
       </c>
       <c r="E71" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="F71" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F71" s="8">
+      <c r="G71" s="8">
         <v>0</v>
-      </c>
-      <c r="G71" s="10">
-        <v>10</v>
       </c>
       <c r="H71" s="10">
         <v>10</v>
       </c>
       <c r="I71" s="10">
+        <v>10</v>
+      </c>
+      <c r="J71" s="10">
         <v>126000</v>
-      </c>
-      <c r="J71" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="L71" s="10" t="s">
+      <c r="L71" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="M71" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="IC71"/>
-    </row>
-    <row r="72" spans="3:237" ht="22.5" customHeight="1">
+      <c r="ID71"/>
+    </row>
+    <row r="72" spans="3:238" ht="22.5" customHeight="1">
       <c r="C72" s="8">
         <v>10700</v>
       </c>
@@ -4880,29 +5363,32 @@
         <v>189</v>
       </c>
       <c r="E72" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="F72" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F72" s="8">
+      <c r="G72" s="8">
         <v>10701</v>
       </c>
-      <c r="G72" s="10">
+      <c r="H72" s="10">
         <v>0</v>
       </c>
-      <c r="H72" s="10">
+      <c r="I72" s="10">
         <v>1</v>
       </c>
-      <c r="I72" s="10">
+      <c r="J72" s="10">
         <v>28800</v>
       </c>
-      <c r="J72" s="11">
+      <c r="K72" s="11">
         <v>1000000</v>
       </c>
-      <c r="K72" s="11" t="s">
+      <c r="L72" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="L72" s="10"/>
-    </row>
-    <row r="73" spans="3:237" ht="20.100000000000001" customHeight="1">
+      <c r="M72" s="10"/>
+    </row>
+    <row r="73" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C73" s="8">
         <v>10701</v>
       </c>
@@ -4910,31 +5396,34 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="F73" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F73" s="8">
+      <c r="G73" s="8">
         <v>10702</v>
-      </c>
-      <c r="G73" s="10">
-        <v>1</v>
       </c>
       <c r="H73" s="10">
         <v>1</v>
       </c>
       <c r="I73" s="10">
+        <v>1</v>
+      </c>
+      <c r="J73" s="10">
         <v>39600</v>
       </c>
-      <c r="J73" s="11">
+      <c r="K73" s="11">
         <v>1500000</v>
       </c>
-      <c r="K73" s="11" t="s">
+      <c r="L73" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="L73" s="10" t="s">
+      <c r="M73" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="74" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C74" s="8">
         <v>10702</v>
       </c>
@@ -4942,32 +5431,35 @@
         <v>191</v>
       </c>
       <c r="E74" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="F74" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F74" s="8">
+      <c r="G74" s="8">
         <v>10703</v>
-      </c>
-      <c r="G74" s="10">
-        <v>2</v>
       </c>
       <c r="H74" s="10">
         <v>2</v>
       </c>
       <c r="I74" s="10">
+        <v>2</v>
+      </c>
+      <c r="J74" s="10">
         <v>50400</v>
       </c>
-      <c r="J74" s="11">
+      <c r="K74" s="11">
         <v>2000000</v>
       </c>
-      <c r="K74" s="11" t="s">
+      <c r="L74" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="L74" s="10" t="s">
+      <c r="M74" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="IC74"/>
-    </row>
-    <row r="75" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID74"/>
+    </row>
+    <row r="75" spans="3:238" ht="19.5" customHeight="1">
       <c r="C75" s="8">
         <v>10703</v>
       </c>
@@ -4975,32 +5467,35 @@
         <v>192</v>
       </c>
       <c r="E75" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="F75" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F75" s="8">
+      <c r="G75" s="8">
         <v>10704</v>
-      </c>
-      <c r="G75" s="10">
-        <v>3</v>
       </c>
       <c r="H75" s="10">
         <v>3</v>
       </c>
       <c r="I75" s="10">
+        <v>3</v>
+      </c>
+      <c r="J75" s="10">
         <v>61200</v>
       </c>
-      <c r="J75" s="11">
+      <c r="K75" s="11">
         <v>2500000</v>
       </c>
-      <c r="K75" s="11" t="s">
+      <c r="L75" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="L75" s="10" t="s">
+      <c r="M75" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="IC75"/>
-    </row>
-    <row r="76" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID75"/>
+    </row>
+    <row r="76" spans="3:238" ht="19.5" customHeight="1">
       <c r="C76" s="8">
         <v>10704</v>
       </c>
@@ -5008,32 +5503,35 @@
         <v>193</v>
       </c>
       <c r="E76" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="F76" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F76" s="8">
+      <c r="G76" s="8">
         <v>10705</v>
-      </c>
-      <c r="G76" s="10">
-        <v>4</v>
       </c>
       <c r="H76" s="10">
         <v>4</v>
       </c>
       <c r="I76" s="10">
+        <v>4</v>
+      </c>
+      <c r="J76" s="10">
         <v>72000</v>
       </c>
-      <c r="J76" s="11">
+      <c r="K76" s="11">
         <v>3000000</v>
       </c>
-      <c r="K76" s="11" t="s">
+      <c r="L76" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="L76" s="10" t="s">
+      <c r="M76" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="IC76"/>
-    </row>
-    <row r="77" spans="3:237" ht="22.5" customHeight="1">
+      <c r="ID76"/>
+    </row>
+    <row r="77" spans="3:238" ht="22.5" customHeight="1">
       <c r="C77" s="8">
         <v>10705</v>
       </c>
@@ -5041,31 +5539,34 @@
         <v>194</v>
       </c>
       <c r="E77" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="F77" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F77" s="8">
+      <c r="G77" s="8">
         <v>10706</v>
-      </c>
-      <c r="G77" s="10">
-        <v>5</v>
       </c>
       <c r="H77" s="10">
         <v>5</v>
       </c>
       <c r="I77" s="10">
+        <v>5</v>
+      </c>
+      <c r="J77" s="10">
         <v>82800</v>
       </c>
-      <c r="J77" s="11">
+      <c r="K77" s="11">
         <v>4000000</v>
       </c>
-      <c r="K77" s="11" t="s">
+      <c r="L77" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="L77" s="10" t="s">
+      <c r="M77" s="10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="78" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="78" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C78" s="8">
         <v>10706</v>
       </c>
@@ -5073,31 +5574,34 @@
         <v>195</v>
       </c>
       <c r="E78" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="F78" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F78" s="8">
+      <c r="G78" s="8">
         <v>10707</v>
-      </c>
-      <c r="G78" s="10">
-        <v>6</v>
       </c>
       <c r="H78" s="10">
         <v>6</v>
       </c>
       <c r="I78" s="10">
+        <v>6</v>
+      </c>
+      <c r="J78" s="10">
         <v>93600</v>
       </c>
-      <c r="J78" s="11">
+      <c r="K78" s="11">
         <v>5000000</v>
       </c>
-      <c r="K78" s="11" t="s">
+      <c r="L78" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="L78" s="10" t="s">
+      <c r="M78" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="79" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C79" s="8">
         <v>10707</v>
       </c>
@@ -5105,32 +5609,35 @@
         <v>196</v>
       </c>
       <c r="E79" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="F79" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F79" s="8">
+      <c r="G79" s="8">
         <v>10708</v>
-      </c>
-      <c r="G79" s="10">
-        <v>7</v>
       </c>
       <c r="H79" s="10">
         <v>7</v>
       </c>
       <c r="I79" s="10">
+        <v>7</v>
+      </c>
+      <c r="J79" s="10">
         <v>104400</v>
       </c>
-      <c r="J79" s="11">
+      <c r="K79" s="11">
         <v>6000000</v>
       </c>
-      <c r="K79" s="11" t="s">
+      <c r="L79" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="L79" s="10" t="s">
+      <c r="M79" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="IC79"/>
-    </row>
-    <row r="80" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID79"/>
+    </row>
+    <row r="80" spans="3:238" ht="19.5" customHeight="1">
       <c r="C80" s="8">
         <v>10708</v>
       </c>
@@ -5138,32 +5645,35 @@
         <v>197</v>
       </c>
       <c r="E80" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="F80" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F80" s="8">
+      <c r="G80" s="8">
         <v>10709</v>
-      </c>
-      <c r="G80" s="10">
-        <v>8</v>
       </c>
       <c r="H80" s="10">
         <v>8</v>
       </c>
       <c r="I80" s="10">
+        <v>8</v>
+      </c>
+      <c r="J80" s="10">
         <v>115200</v>
       </c>
-      <c r="J80" s="11">
+      <c r="K80" s="11">
         <v>7000000</v>
       </c>
-      <c r="K80" s="11" t="s">
+      <c r="L80" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="L80" s="10" t="s">
+      <c r="M80" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="IC80"/>
-    </row>
-    <row r="81" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID80"/>
+    </row>
+    <row r="81" spans="3:238" ht="19.5" customHeight="1">
       <c r="C81" s="8">
         <v>10709</v>
       </c>
@@ -5171,32 +5681,35 @@
         <v>198</v>
       </c>
       <c r="E81" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="F81" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F81" s="8">
+      <c r="G81" s="8">
         <v>10710</v>
-      </c>
-      <c r="G81" s="10">
-        <v>9</v>
       </c>
       <c r="H81" s="10">
         <v>9</v>
       </c>
       <c r="I81" s="10">
+        <v>9</v>
+      </c>
+      <c r="J81" s="10">
         <v>126000</v>
       </c>
-      <c r="J81" s="11">
+      <c r="K81" s="11">
         <v>8000000</v>
       </c>
-      <c r="K81" s="11" t="s">
+      <c r="L81" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="L81" s="10" t="s">
+      <c r="M81" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="IC81"/>
-    </row>
-    <row r="82" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID81"/>
+    </row>
+    <row r="82" spans="3:238" ht="19.5" customHeight="1">
       <c r="C82" s="8">
         <v>10710</v>
       </c>
@@ -5204,32 +5717,35 @@
         <v>199</v>
       </c>
       <c r="E82" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="F82" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F82" s="8">
+      <c r="G82" s="8">
         <v>0</v>
-      </c>
-      <c r="G82" s="10">
-        <v>10</v>
       </c>
       <c r="H82" s="10">
         <v>10</v>
       </c>
       <c r="I82" s="10">
+        <v>10</v>
+      </c>
+      <c r="J82" s="10">
         <v>126000</v>
-      </c>
-      <c r="J82" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="K82" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="L82" s="10" t="s">
+      <c r="L82" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="M82" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="IC82"/>
-    </row>
-    <row r="83" spans="3:237" ht="22.5" customHeight="1">
+      <c r="ID82"/>
+    </row>
+    <row r="83" spans="3:238" ht="22.5" customHeight="1">
       <c r="C83" s="8">
         <v>10800</v>
       </c>
@@ -5237,29 +5753,32 @@
         <v>200</v>
       </c>
       <c r="E83" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="F83" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F83" s="8">
+      <c r="G83" s="8">
         <v>10801</v>
       </c>
-      <c r="G83" s="10">
+      <c r="H83" s="10">
         <v>0</v>
       </c>
-      <c r="H83" s="10">
+      <c r="I83" s="10">
         <v>1</v>
       </c>
-      <c r="I83" s="10">
+      <c r="J83" s="10">
         <v>28800</v>
       </c>
-      <c r="J83" s="11">
+      <c r="K83" s="11">
         <v>1000000</v>
       </c>
-      <c r="K83" s="11" t="s">
+      <c r="L83" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="L83" s="10"/>
-    </row>
-    <row r="84" spans="3:237" ht="20.100000000000001" customHeight="1">
+      <c r="M83" s="10"/>
+    </row>
+    <row r="84" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C84" s="8">
         <v>10801</v>
       </c>
@@ -5267,31 +5786,34 @@
         <v>201</v>
       </c>
       <c r="E84" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="F84" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F84" s="8">
+      <c r="G84" s="8">
         <v>10802</v>
-      </c>
-      <c r="G84" s="10">
-        <v>1</v>
       </c>
       <c r="H84" s="10">
         <v>1</v>
       </c>
       <c r="I84" s="10">
+        <v>1</v>
+      </c>
+      <c r="J84" s="10">
         <v>39600</v>
       </c>
-      <c r="J84" s="11">
+      <c r="K84" s="11">
         <v>1500000</v>
       </c>
-      <c r="K84" s="11" t="s">
+      <c r="L84" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="L84" s="10" t="s">
+      <c r="M84" s="10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="85" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="85" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C85" s="8">
         <v>10802</v>
       </c>
@@ -5299,32 +5821,35 @@
         <v>202</v>
       </c>
       <c r="E85" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="F85" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F85" s="8">
+      <c r="G85" s="8">
         <v>10803</v>
-      </c>
-      <c r="G85" s="10">
-        <v>2</v>
       </c>
       <c r="H85" s="10">
         <v>2</v>
       </c>
       <c r="I85" s="10">
+        <v>2</v>
+      </c>
+      <c r="J85" s="10">
         <v>50400</v>
       </c>
-      <c r="J85" s="11">
+      <c r="K85" s="11">
         <v>2000000</v>
       </c>
-      <c r="K85" s="11" t="s">
+      <c r="L85" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="L85" s="10" t="s">
+      <c r="M85" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="IC85"/>
-    </row>
-    <row r="86" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID85"/>
+    </row>
+    <row r="86" spans="3:238" ht="19.5" customHeight="1">
       <c r="C86" s="8">
         <v>10803</v>
       </c>
@@ -5332,32 +5857,35 @@
         <v>203</v>
       </c>
       <c r="E86" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="F86" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F86" s="8">
+      <c r="G86" s="8">
         <v>10804</v>
-      </c>
-      <c r="G86" s="10">
-        <v>3</v>
       </c>
       <c r="H86" s="10">
         <v>3</v>
       </c>
       <c r="I86" s="10">
+        <v>3</v>
+      </c>
+      <c r="J86" s="10">
         <v>61200</v>
       </c>
-      <c r="J86" s="11">
+      <c r="K86" s="11">
         <v>2500000</v>
       </c>
-      <c r="K86" s="11" t="s">
+      <c r="L86" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="L86" s="10" t="s">
+      <c r="M86" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="IC86"/>
-    </row>
-    <row r="87" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID86"/>
+    </row>
+    <row r="87" spans="3:238" ht="19.5" customHeight="1">
       <c r="C87" s="8">
         <v>10804</v>
       </c>
@@ -5365,32 +5893,35 @@
         <v>204</v>
       </c>
       <c r="E87" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="F87" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F87" s="8">
+      <c r="G87" s="8">
         <v>10805</v>
-      </c>
-      <c r="G87" s="10">
-        <v>4</v>
       </c>
       <c r="H87" s="10">
         <v>4</v>
       </c>
       <c r="I87" s="10">
+        <v>4</v>
+      </c>
+      <c r="J87" s="10">
         <v>72000</v>
       </c>
-      <c r="J87" s="11">
+      <c r="K87" s="11">
         <v>3000000</v>
       </c>
-      <c r="K87" s="11" t="s">
+      <c r="L87" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="L87" s="10" t="s">
+      <c r="M87" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="IC87"/>
-    </row>
-    <row r="88" spans="3:237" ht="22.5" customHeight="1">
+      <c r="ID87"/>
+    </row>
+    <row r="88" spans="3:238" ht="22.5" customHeight="1">
       <c r="C88" s="8">
         <v>10805</v>
       </c>
@@ -5398,31 +5929,34 @@
         <v>205</v>
       </c>
       <c r="E88" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="F88" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F88" s="8">
+      <c r="G88" s="8">
         <v>10806</v>
-      </c>
-      <c r="G88" s="10">
-        <v>5</v>
       </c>
       <c r="H88" s="10">
         <v>5</v>
       </c>
       <c r="I88" s="10">
+        <v>5</v>
+      </c>
+      <c r="J88" s="10">
         <v>82800</v>
       </c>
-      <c r="J88" s="11">
+      <c r="K88" s="11">
         <v>4000000</v>
       </c>
-      <c r="K88" s="11" t="s">
+      <c r="L88" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="L88" s="10" t="s">
+      <c r="M88" s="10" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="89" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="89" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C89" s="8">
         <v>10806</v>
       </c>
@@ -5430,31 +5964,34 @@
         <v>206</v>
       </c>
       <c r="E89" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F89" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F89" s="8">
+      <c r="G89" s="8">
         <v>10807</v>
-      </c>
-      <c r="G89" s="10">
-        <v>6</v>
       </c>
       <c r="H89" s="10">
         <v>6</v>
       </c>
       <c r="I89" s="10">
+        <v>6</v>
+      </c>
+      <c r="J89" s="10">
         <v>93600</v>
       </c>
-      <c r="J89" s="11">
+      <c r="K89" s="11">
         <v>5000000</v>
       </c>
-      <c r="K89" s="11" t="s">
+      <c r="L89" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="L89" s="10" t="s">
+      <c r="M89" s="10" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="90" spans="3:237" ht="20.100000000000001" customHeight="1">
+    <row r="90" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C90" s="8">
         <v>10807</v>
       </c>
@@ -5462,32 +5999,35 @@
         <v>207</v>
       </c>
       <c r="E90" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="F90" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F90" s="8">
+      <c r="G90" s="8">
         <v>10808</v>
-      </c>
-      <c r="G90" s="10">
-        <v>7</v>
       </c>
       <c r="H90" s="10">
         <v>7</v>
       </c>
       <c r="I90" s="10">
+        <v>7</v>
+      </c>
+      <c r="J90" s="10">
         <v>104400</v>
       </c>
-      <c r="J90" s="11">
+      <c r="K90" s="11">
         <v>6000000</v>
       </c>
-      <c r="K90" s="11" t="s">
+      <c r="L90" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="L90" s="10" t="s">
+      <c r="M90" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="IC90"/>
-    </row>
-    <row r="91" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID90"/>
+    </row>
+    <row r="91" spans="3:238" ht="19.5" customHeight="1">
       <c r="C91" s="8">
         <v>10808</v>
       </c>
@@ -5495,32 +6035,35 @@
         <v>208</v>
       </c>
       <c r="E91" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="F91" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F91" s="8">
+      <c r="G91" s="8">
         <v>10809</v>
-      </c>
-      <c r="G91" s="10">
-        <v>8</v>
       </c>
       <c r="H91" s="10">
         <v>8</v>
       </c>
       <c r="I91" s="10">
+        <v>8</v>
+      </c>
+      <c r="J91" s="10">
         <v>115200</v>
       </c>
-      <c r="J91" s="11">
+      <c r="K91" s="11">
         <v>7000000</v>
       </c>
-      <c r="K91" s="11" t="s">
+      <c r="L91" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="L91" s="10" t="s">
+      <c r="M91" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="IC91"/>
-    </row>
-    <row r="92" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID91"/>
+    </row>
+    <row r="92" spans="3:238" ht="19.5" customHeight="1">
       <c r="C92" s="8">
         <v>10809</v>
       </c>
@@ -5528,32 +6071,35 @@
         <v>209</v>
       </c>
       <c r="E92" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="F92" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F92" s="8">
+      <c r="G92" s="8">
         <v>10810</v>
-      </c>
-      <c r="G92" s="10">
-        <v>9</v>
       </c>
       <c r="H92" s="10">
         <v>9</v>
       </c>
       <c r="I92" s="10">
+        <v>9</v>
+      </c>
+      <c r="J92" s="10">
         <v>126000</v>
       </c>
-      <c r="J92" s="11">
+      <c r="K92" s="11">
         <v>8000000</v>
       </c>
-      <c r="K92" s="11" t="s">
+      <c r="L92" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="L92" s="10" t="s">
+      <c r="M92" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="IC92"/>
-    </row>
-    <row r="93" spans="3:237" ht="19.5" customHeight="1">
+      <c r="ID92"/>
+    </row>
+    <row r="93" spans="3:238" ht="19.5" customHeight="1">
       <c r="C93" s="8">
         <v>10810</v>
       </c>
@@ -5561,30 +6107,33 @@
         <v>210</v>
       </c>
       <c r="E93" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="F93" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F93" s="8">
+      <c r="G93" s="8">
         <v>0</v>
-      </c>
-      <c r="G93" s="10">
-        <v>10</v>
       </c>
       <c r="H93" s="10">
         <v>10</v>
       </c>
       <c r="I93" s="10">
+        <v>10</v>
+      </c>
+      <c r="J93" s="10">
         <v>126000</v>
-      </c>
-      <c r="J93" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="K93" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="L93" s="10" t="s">
+      <c r="L93" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="M93" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="IC93"/>
+      <c r="ID93"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/Excel/UnionKeJiConfig.xlsx
+++ b/Excel/UnionKeJiConfig.xlsx
@@ -1,45 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC235C6-32C3-44E2-ABF6-1C5900711B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12795"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnionKeJiProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="M3" authorId="0">
+    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>作者:
 10.生命值
@@ -96,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="217">
   <si>
     <t>Id</t>
   </si>
@@ -167,9 +160,6 @@
     <t>经验科技0级</t>
   </si>
   <si>
-    <t>Experience Technology Level 0</t>
-  </si>
-  <si>
     <t>keji_1</t>
   </si>
   <si>
@@ -179,9 +169,6 @@
     <t>经验科技1级</t>
   </si>
   <si>
-    <t>Experience Technology Level 1</t>
-  </si>
-  <si>
     <t>16;750@10000163;15</t>
   </si>
   <si>
@@ -191,9 +178,6 @@
     <t>经验科技2级</t>
   </si>
   <si>
-    <t>Experience Technology Level 2</t>
-  </si>
-  <si>
     <t>16;1000@10000163;20</t>
   </si>
   <si>
@@ -203,9 +187,6 @@
     <t>经验科技3级</t>
   </si>
   <si>
-    <t>Experience Technology Level 3</t>
-  </si>
-  <si>
     <t>16;1300@10000163;25</t>
   </si>
   <si>
@@ -215,9 +196,6 @@
     <t>经验科技4级</t>
   </si>
   <si>
-    <t>Experience Technology Level 4</t>
-  </si>
-  <si>
     <t>16;1600@10000163;30</t>
   </si>
   <si>
@@ -227,9 +205,6 @@
     <t>经验科技5级</t>
   </si>
   <si>
-    <t>Experience Technology Level 5</t>
-  </si>
-  <si>
     <t>16;2000@10000163;35</t>
   </si>
   <si>
@@ -239,9 +214,6 @@
     <t>经验科技6级</t>
   </si>
   <si>
-    <t>Experience Technology Level 6</t>
-  </si>
-  <si>
     <t>16;2400@10000163;40</t>
   </si>
   <si>
@@ -251,9 +223,6 @@
     <t>经验科技7级</t>
   </si>
   <si>
-    <t>Experience Technology Level 7</t>
-  </si>
-  <si>
     <t>16;2800@10000163;45</t>
   </si>
   <si>
@@ -263,9 +232,6 @@
     <t>经验科技8级</t>
   </si>
   <si>
-    <t>Experience Technology Level 8</t>
-  </si>
-  <si>
     <t>16;3200@10000163;50</t>
   </si>
   <si>
@@ -275,9 +241,6 @@
     <t>经验科技9级</t>
   </si>
   <si>
-    <t>Experience Technology Level 9</t>
-  </si>
-  <si>
     <t>16;3600@10000163;60</t>
   </si>
   <si>
@@ -287,9 +250,6 @@
     <t>经验科技10级</t>
   </si>
   <si>
-    <t>Experience Technology Level 10</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
@@ -299,707 +259,502 @@
     <t>金币科技0级</t>
   </si>
   <si>
-    <t>Gold technology level 0</t>
-  </si>
-  <si>
     <t>keji_2</t>
   </si>
   <si>
     <t>金币科技1级</t>
   </si>
   <si>
-    <t>Gold technology level 1</t>
-  </si>
-  <si>
     <t>220203;0.01</t>
   </si>
   <si>
     <t>金币科技2级</t>
   </si>
   <si>
-    <t>Gold technology level 2</t>
-  </si>
-  <si>
     <t>220203;0.02</t>
   </si>
   <si>
     <t>金币科技3级</t>
   </si>
   <si>
-    <t>Gold technology level 3</t>
-  </si>
-  <si>
     <t>220203;0.03</t>
   </si>
   <si>
     <t>金币科技4级</t>
   </si>
   <si>
-    <t>Gold technology level 4</t>
-  </si>
-  <si>
     <t>220203;0.04</t>
   </si>
   <si>
     <t>金币科技5级</t>
   </si>
   <si>
-    <t>Gold technology level 5</t>
-  </si>
-  <si>
     <t>220203;0.05</t>
   </si>
   <si>
     <t>金币科技6级</t>
   </si>
   <si>
-    <t>Gold technology level 6</t>
-  </si>
-  <si>
     <t>220203;0.06</t>
   </si>
   <si>
     <t>金币科技7级</t>
   </si>
   <si>
-    <t>Gold technology level 7</t>
-  </si>
-  <si>
     <t>220203;0.07</t>
   </si>
   <si>
     <t>金币科技8级</t>
   </si>
   <si>
-    <t>Gold technology level 8</t>
-  </si>
-  <si>
     <t>220203;0.08</t>
   </si>
   <si>
     <t>金币科技9级</t>
   </si>
   <si>
-    <t>Gold technology level 9</t>
-  </si>
-  <si>
     <t>220203;0.09</t>
   </si>
   <si>
     <t>金币科技10级</t>
   </si>
   <si>
-    <t>Gold technology level 10</t>
-  </si>
-  <si>
     <t>220203;0.10</t>
   </si>
   <si>
     <t>怪之攻伤0级</t>
   </si>
   <si>
-    <t xml:space="preserve">Monster Damage Level 0 </t>
-  </si>
-  <si>
     <t>keji_3</t>
   </si>
   <si>
     <t>怪之攻伤1级</t>
   </si>
   <si>
-    <t>Monster Damage Level 1</t>
-  </si>
-  <si>
     <t>223003;0.01</t>
   </si>
   <si>
     <t>怪之攻伤2级</t>
   </si>
   <si>
-    <t>Monster Damage Level 2</t>
-  </si>
-  <si>
     <t>223003;0.02</t>
   </si>
   <si>
     <t>怪之攻伤3级</t>
   </si>
   <si>
-    <t>Monster Damage Level 3</t>
-  </si>
-  <si>
     <t>223003;0.03</t>
   </si>
   <si>
     <t>怪之攻伤4级</t>
   </si>
   <si>
-    <t>Monster Damage Level 4</t>
-  </si>
-  <si>
     <t>223003;0.04</t>
   </si>
   <si>
     <t>怪之攻伤5级</t>
   </si>
   <si>
-    <t>Monster Damage Level 5</t>
-  </si>
-  <si>
     <t>223003;0.05</t>
   </si>
   <si>
     <t>怪之攻伤6级</t>
   </si>
   <si>
-    <t>Monster Damage Level 6</t>
-  </si>
-  <si>
     <t>223003;0.06</t>
   </si>
   <si>
     <t>怪之攻伤7级</t>
   </si>
   <si>
-    <t>Monster Damage Level 7</t>
-  </si>
-  <si>
     <t>223003;0.07</t>
   </si>
   <si>
     <t>怪之攻伤8级</t>
   </si>
   <si>
-    <t>Monster Damage Level 8</t>
-  </si>
-  <si>
     <t>223003;0.08</t>
   </si>
   <si>
     <t>怪之攻伤9级</t>
   </si>
   <si>
-    <t>Monster Damage Level 9</t>
-  </si>
-  <si>
     <t>223003;0.09</t>
   </si>
   <si>
     <t>怪之攻伤10级</t>
   </si>
   <si>
-    <t>Monster Damage Level 10</t>
-  </si>
-  <si>
     <t>223003;0.10</t>
   </si>
   <si>
     <t>怪之技伤0级</t>
   </si>
   <si>
-    <t>Monster Skill Level 0</t>
-  </si>
-  <si>
     <t>keji_4</t>
   </si>
   <si>
     <t>怪之技伤1级</t>
   </si>
   <si>
-    <t>Monster Skill Level 1</t>
-  </si>
-  <si>
     <t>223103;0.01</t>
   </si>
   <si>
     <t>怪之技伤2级</t>
   </si>
   <si>
-    <t>Monster Skill Level 2</t>
-  </si>
-  <si>
     <t>223103;0.02</t>
   </si>
   <si>
     <t>怪之技伤3级</t>
   </si>
   <si>
-    <t>Monster Skill Level 3</t>
-  </si>
-  <si>
     <t>223103;0.03</t>
   </si>
   <si>
     <t>怪之技伤4级</t>
   </si>
   <si>
-    <t>Monster Skill Level 4</t>
-  </si>
-  <si>
     <t>223103;0.04</t>
   </si>
   <si>
     <t>怪之技伤5级</t>
   </si>
   <si>
-    <t>Monster Skill Level 5</t>
-  </si>
-  <si>
     <t>223103;0.05</t>
   </si>
   <si>
     <t>怪之技伤6级</t>
   </si>
   <si>
-    <t>Monster Skill Level 6</t>
-  </si>
-  <si>
     <t>223103;0.06</t>
   </si>
   <si>
     <t>怪之技伤7级</t>
   </si>
   <si>
-    <t>Monster Skill Level 7</t>
-  </si>
-  <si>
     <t>223103;0.07</t>
   </si>
   <si>
     <t>怪之技伤8级</t>
   </si>
   <si>
-    <t>Monster Skill Level 8</t>
-  </si>
-  <si>
     <t>223103;0.08</t>
   </si>
   <si>
     <t>怪之技伤9级</t>
   </si>
   <si>
-    <t>Monster Skill Level 9</t>
-  </si>
-  <si>
     <t>223103;0.09</t>
   </si>
   <si>
     <t>怪之技伤10级</t>
   </si>
   <si>
-    <t>Monster Skill Level 10</t>
-  </si>
-  <si>
     <t>223103;0.10</t>
   </si>
   <si>
     <t>怪之攻防0级</t>
   </si>
   <si>
-    <t>Monster Defence Level 0</t>
-  </si>
-  <si>
     <t>keji_5</t>
   </si>
   <si>
     <t>怪之攻防1级</t>
   </si>
   <si>
-    <t>Monster Defence Level 1</t>
-  </si>
-  <si>
     <t>223203;0.01</t>
   </si>
   <si>
     <t>怪之攻防2级</t>
   </si>
   <si>
-    <t>Monster Defence Level 2</t>
-  </si>
-  <si>
     <t>223203;0.02</t>
   </si>
   <si>
     <t>怪之攻防3级</t>
   </si>
   <si>
-    <t>Monster Defence Level 3</t>
-  </si>
-  <si>
     <t>223203;0.03</t>
   </si>
   <si>
     <t>怪之攻防4级</t>
   </si>
   <si>
-    <t>Monster Defence Level 4</t>
-  </si>
-  <si>
     <t>223203;0.04</t>
   </si>
   <si>
     <t>怪之攻防5级</t>
   </si>
   <si>
-    <t>Monster Defence Level 5</t>
-  </si>
-  <si>
     <t>223203;0.05</t>
   </si>
   <si>
     <t>怪之攻防6级</t>
   </si>
   <si>
-    <t>Monster Defence Level 6</t>
-  </si>
-  <si>
     <t>223203;0.06</t>
   </si>
   <si>
     <t>怪之攻防7级</t>
   </si>
   <si>
-    <t>Monster Defence Level 7</t>
-  </si>
-  <si>
     <t>223203;0.07</t>
   </si>
   <si>
     <t>怪之攻防8级</t>
   </si>
   <si>
-    <t>Monster Defence Level 8</t>
-  </si>
-  <si>
     <t>223203;0.08</t>
   </si>
   <si>
     <t>怪之攻防9级</t>
   </si>
   <si>
-    <t>Monster Defence Level 9</t>
-  </si>
-  <si>
     <t>223203;0.09</t>
   </si>
   <si>
     <t>怪之攻防10级</t>
   </si>
   <si>
-    <t>Monster Defence Level 10</t>
-  </si>
-  <si>
     <t>223203;0.10</t>
   </si>
   <si>
     <t>怪之技防0级</t>
   </si>
   <si>
-    <t>Monster Arts Defence Level 0</t>
-  </si>
-  <si>
     <t>keji_6</t>
   </si>
   <si>
     <t>怪之技防1级</t>
   </si>
   <si>
-    <t>Monster Arts Defence Level 1</t>
-  </si>
-  <si>
     <t>223303;0.01</t>
   </si>
   <si>
     <t>怪之技防2级</t>
   </si>
   <si>
-    <t>Monster Arts Defence Level 2</t>
-  </si>
-  <si>
     <t>223303;0.02</t>
   </si>
   <si>
     <t>怪之技防3级</t>
   </si>
   <si>
-    <t>Monster Arts Defence Level 3</t>
-  </si>
-  <si>
     <t>223303;0.03</t>
   </si>
   <si>
     <t>怪之技防4级</t>
   </si>
   <si>
-    <t>Monster Arts Defence Level 4</t>
-  </si>
-  <si>
     <t>223303;0.04</t>
   </si>
   <si>
     <t>怪之技防5级</t>
   </si>
   <si>
-    <t>Monster Arts Defence Level 5</t>
-  </si>
-  <si>
     <t>223303;0.05</t>
   </si>
   <si>
     <t>怪之技防6级</t>
   </si>
   <si>
-    <t>Monster Arts Defence Level 6</t>
-  </si>
-  <si>
     <t>223303;0.06</t>
   </si>
   <si>
     <t>怪之技防7级</t>
   </si>
   <si>
-    <t>Monster Arts Defence Level 7</t>
-  </si>
-  <si>
     <t>223303;0.07</t>
   </si>
   <si>
     <t>怪之技防8级</t>
   </si>
   <si>
-    <t>Monster Arts Defence Level 8</t>
-  </si>
-  <si>
     <t>223303;0.08</t>
   </si>
   <si>
     <t>怪之技防9级</t>
   </si>
   <si>
-    <t>Monster Arts Defence Level 9</t>
-  </si>
-  <si>
     <t>223303;0.09</t>
   </si>
   <si>
     <t>怪之技防10级</t>
   </si>
   <si>
-    <t>Monster Arts Defence Level 10</t>
-  </si>
-  <si>
     <t>223303;0.10</t>
   </si>
   <si>
     <t>玩家攻减0级</t>
   </si>
   <si>
-    <t>Player Defence level 0</t>
-  </si>
-  <si>
     <t>keji_7</t>
   </si>
   <si>
     <t>玩家攻减1级</t>
   </si>
   <si>
-    <t>Player Defence level 1</t>
-  </si>
-  <si>
     <t>205703;0.01</t>
   </si>
   <si>
     <t>玩家攻减2级</t>
   </si>
   <si>
-    <t>Player Defence level 2</t>
-  </si>
-  <si>
     <t>205703;0.02</t>
   </si>
   <si>
     <t>玩家攻减3级</t>
   </si>
   <si>
-    <t>Player Defence level 3</t>
-  </si>
-  <si>
     <t>205703;0.03</t>
   </si>
   <si>
     <t>玩家攻减4级</t>
   </si>
   <si>
-    <t>Player Defence level 4</t>
-  </si>
-  <si>
     <t>205703;0.04</t>
   </si>
   <si>
     <t>玩家攻减5级</t>
   </si>
   <si>
-    <t>Player Defence level 5</t>
-  </si>
-  <si>
     <t>205703;0.05</t>
   </si>
   <si>
     <t>玩家攻减6级</t>
   </si>
   <si>
-    <t>Player Defence level 6</t>
-  </si>
-  <si>
     <t>205703;0.06</t>
   </si>
   <si>
     <t>玩家攻减7级</t>
   </si>
   <si>
-    <t>Player Defence level 7</t>
-  </si>
-  <si>
     <t>205703;0.07</t>
   </si>
   <si>
     <t>玩家攻减8级</t>
   </si>
   <si>
-    <t>Player Defence level 8</t>
-  </si>
-  <si>
     <t>205703;0.08</t>
   </si>
   <si>
     <t>玩家攻减9级</t>
   </si>
   <si>
-    <t>Player Defence level 9</t>
-  </si>
-  <si>
     <t>205703;0.09</t>
   </si>
   <si>
     <t>玩家攻减10级</t>
   </si>
   <si>
-    <t>Player Defence level 10</t>
-  </si>
-  <si>
     <t>205703;0.10</t>
   </si>
   <si>
     <t>玩家技减0级</t>
   </si>
   <si>
-    <t>Player Arts Defence level 0</t>
-  </si>
-  <si>
     <t>keji_8</t>
   </si>
   <si>
     <t>玩家技减1级</t>
   </si>
   <si>
-    <t>Player Arts Defence level 1</t>
-  </si>
-  <si>
     <t>205803;0.01</t>
   </si>
   <si>
     <t>玩家技减2级</t>
   </si>
   <si>
-    <t>Player Arts Defence level 2</t>
-  </si>
-  <si>
     <t>205803;0.02</t>
   </si>
   <si>
     <t>玩家技减3级</t>
   </si>
   <si>
-    <t>Player Arts Defence level 3</t>
-  </si>
-  <si>
     <t>205803;0.03</t>
   </si>
   <si>
     <t>玩家技减4级</t>
   </si>
   <si>
-    <t>Player Arts Defence level 4</t>
-  </si>
-  <si>
     <t>205803;0.04</t>
   </si>
   <si>
     <t>玩家技减5级</t>
   </si>
   <si>
-    <t>Player Arts Defence level 5</t>
-  </si>
-  <si>
     <t>205803;0.05</t>
   </si>
   <si>
     <t>玩家技减6级</t>
   </si>
   <si>
-    <t>Player Arts Defence level 6</t>
-  </si>
-  <si>
     <t>205803;0.06</t>
   </si>
   <si>
     <t>玩家技减7级</t>
   </si>
   <si>
-    <t>Player Arts Defence level 7</t>
-  </si>
-  <si>
     <t>205803;0.07</t>
   </si>
   <si>
     <t>玩家技减8级</t>
   </si>
   <si>
-    <t>Player Arts Defence level 8</t>
-  </si>
-  <si>
     <t>205803;0.08</t>
   </si>
   <si>
     <t>玩家技减9级</t>
   </si>
   <si>
-    <t>Player Arts Defence level 9</t>
-  </si>
-  <si>
     <t>205803;0.09</t>
   </si>
   <si>
     <t>玩家技减10级</t>
   </si>
   <si>
-    <t>Player Arts Defence level 10</t>
-  </si>
-  <si>
     <t>205803;0.10</t>
+  </si>
+  <si>
+    <t>Monster Damage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster Skill</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster Defence</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster Arts Defence</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player Defence</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player Arts Defence</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Experience</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1010,12 +765,14 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1023,179 +780,37 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1220,194 +835,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="15">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1501,251 +930,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1775,57 +962,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
@@ -1898,6 +1038,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2968,12 +2111,12 @@
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C1:ID93"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
@@ -2989,12 +2132,12 @@
     <col min="14" max="238" width="8.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25"/>
-    <row r="2" customHeight="1" spans="4:5">
+    <row r="1" spans="3:238" s="1" customFormat="1" ht="14.25"/>
+    <row r="2" spans="3:238" ht="13.5" customHeight="1">
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="3:13">
+    <row r="3" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -3029,7 +2172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:13">
+    <row r="4" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -3064,7 +2207,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:13">
+    <row r="5" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C5" s="4" t="s">
         <v>20</v>
       </c>
@@ -3099,7 +2242,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="3:13">
+    <row r="6" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C6" s="8">
         <v>10100</v>
       </c>
@@ -3107,10 +2250,10 @@
         <v>22</v>
       </c>
       <c r="E6" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>23</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>24</v>
       </c>
       <c r="G6" s="8">
         <v>10101</v>
@@ -3128,22 +2271,22 @@
         <v>1000000</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M6" s="11"/>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="3:13">
+    <row r="7" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C7" s="8">
         <v>10101</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>27</v>
+        <v>215</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" s="8">
         <v>10102</v>
@@ -3161,24 +2304,24 @@
         <v>1500000</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" ht="20.1" customHeight="1" spans="3:238">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C8" s="8">
         <v>10102</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>31</v>
+        <v>215</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G8" s="8">
         <v>10103</v>
@@ -3196,25 +2339,25 @@
         <v>2000000</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="ID8"/>
     </row>
-    <row r="9" ht="19.5" customHeight="1" spans="3:238">
+    <row r="9" spans="3:238" ht="19.5" customHeight="1">
       <c r="C9" s="8">
         <v>10103</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>35</v>
+        <v>215</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G9" s="8">
         <v>10104</v>
@@ -3232,25 +2375,25 @@
         <v>2500000</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="ID9"/>
     </row>
-    <row r="10" ht="19.5" customHeight="1" spans="3:238">
+    <row r="10" spans="3:238" ht="19.5" customHeight="1">
       <c r="C10" s="8">
         <v>10104</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>39</v>
+        <v>215</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" s="8">
         <v>10105</v>
@@ -3268,25 +2411,25 @@
         <v>3000000</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="ID10"/>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="3:13">
+    <row r="11" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C11" s="8">
         <v>10105</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>43</v>
+        <v>215</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G11" s="8">
         <v>10106</v>
@@ -3304,24 +2447,24 @@
         <v>4000000</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" ht="20.1" customHeight="1" spans="3:238">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C12" s="8">
         <v>10106</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>47</v>
+        <v>215</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G12" s="8">
         <v>10107</v>
@@ -3339,25 +2482,25 @@
         <v>5000000</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="ID12"/>
     </row>
-    <row r="13" ht="19.5" customHeight="1" spans="3:238">
+    <row r="13" spans="3:238" ht="19.5" customHeight="1">
       <c r="C13" s="8">
         <v>10107</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>51</v>
+        <v>215</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G13" s="8">
         <v>10108</v>
@@ -3375,25 +2518,25 @@
         <v>6000000</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="ID13"/>
     </row>
-    <row r="14" ht="19.5" customHeight="1" spans="3:238">
+    <row r="14" spans="3:238" ht="19.5" customHeight="1">
       <c r="C14" s="8">
         <v>10108</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G14" s="8">
         <v>10109</v>
@@ -3411,25 +2554,25 @@
         <v>7000000</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="ID14"/>
     </row>
-    <row r="15" ht="19.5" customHeight="1" spans="3:238">
+    <row r="15" spans="3:238" ht="19.5" customHeight="1">
       <c r="C15" s="8">
         <v>10109</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>59</v>
+        <v>215</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G15" s="8">
         <v>10110</v>
@@ -3447,25 +2590,25 @@
         <v>8000000</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="ID15"/>
     </row>
-    <row r="16" ht="19.5" customHeight="1" spans="3:238">
+    <row r="16" spans="3:238" ht="19.5" customHeight="1">
       <c r="C16" s="8">
         <v>10110</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>63</v>
+        <v>215</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G16" s="8">
         <v>0</v>
@@ -3480,28 +2623,28 @@
         <v>126000</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="ID16"/>
     </row>
-    <row r="17" ht="22.5" customHeight="1" spans="3:13">
+    <row r="17" spans="3:238" ht="22.5" customHeight="1">
       <c r="C17" s="8">
         <v>10200</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G17" s="8">
         <v>10201</v>
@@ -3519,22 +2662,22 @@
         <v>1000000</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M17" s="11"/>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="3:13">
+    <row r="18" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C18" s="8">
         <v>10201</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>70</v>
+        <v>216</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G18" s="8">
         <v>10202</v>
@@ -3552,24 +2695,24 @@
         <v>1500000</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" ht="20.1" customHeight="1" spans="3:238">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C19" s="8">
         <v>10202</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>73</v>
+        <v>216</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G19" s="8">
         <v>10203</v>
@@ -3587,25 +2730,25 @@
         <v>2000000</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="ID19"/>
     </row>
-    <row r="20" ht="19.5" customHeight="1" spans="3:238">
+    <row r="20" spans="3:238" ht="19.5" customHeight="1">
       <c r="C20" s="8">
         <v>10203</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>76</v>
+        <v>216</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G20" s="8">
         <v>10204</v>
@@ -3623,25 +2766,25 @@
         <v>2500000</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="ID20"/>
     </row>
-    <row r="21" ht="19.5" customHeight="1" spans="3:238">
+    <row r="21" spans="3:238" ht="19.5" customHeight="1">
       <c r="C21" s="8">
         <v>10204</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>79</v>
+        <v>216</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G21" s="8">
         <v>10205</v>
@@ -3659,25 +2802,25 @@
         <v>3000000</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="ID21"/>
     </row>
-    <row r="22" ht="22.5" customHeight="1" spans="3:13">
+    <row r="22" spans="3:238" ht="22.5" customHeight="1">
       <c r="C22" s="8">
         <v>10205</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G22" s="8">
         <v>10206</v>
@@ -3695,24 +2838,24 @@
         <v>4000000</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" ht="20.1" customHeight="1" spans="3:13">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C23" s="8">
         <v>10206</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>85</v>
+        <v>216</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G23" s="8">
         <v>10207</v>
@@ -3730,24 +2873,24 @@
         <v>5000000</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" ht="20.1" customHeight="1" spans="3:238">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C24" s="8">
         <v>10207</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>88</v>
+        <v>216</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G24" s="8">
         <v>10208</v>
@@ -3765,25 +2908,25 @@
         <v>6000000</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="ID24"/>
     </row>
-    <row r="25" ht="19.5" customHeight="1" spans="3:238">
+    <row r="25" spans="3:238" ht="19.5" customHeight="1">
       <c r="C25" s="8">
         <v>10208</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>91</v>
+        <v>216</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G25" s="8">
         <v>10209</v>
@@ -3801,25 +2944,25 @@
         <v>7000000</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="ID25"/>
     </row>
-    <row r="26" ht="19.5" customHeight="1" spans="3:238">
+    <row r="26" spans="3:238" ht="19.5" customHeight="1">
       <c r="C26" s="8">
         <v>10209</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>94</v>
+        <v>216</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G26" s="8">
         <v>10210</v>
@@ -3837,25 +2980,25 @@
         <v>8000000</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M26" s="11" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="ID26"/>
     </row>
-    <row r="27" ht="19.5" customHeight="1" spans="3:238">
+    <row r="27" spans="3:238" ht="19.5" customHeight="1">
       <c r="C27" s="8">
         <v>10210</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>97</v>
+        <v>216</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G27" s="8">
         <v>0</v>
@@ -3870,28 +3013,28 @@
         <v>126000</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="M27" s="11" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="ID27"/>
     </row>
-    <row r="28" ht="22.5" customHeight="1" spans="3:13">
+    <row r="28" spans="3:238" ht="22.5" customHeight="1">
       <c r="C28" s="8">
         <v>10300</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>100</v>
+        <v>209</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="G28" s="8">
         <v>10301</v>
@@ -3909,22 +3052,22 @@
         <v>1000000</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M28" s="11"/>
     </row>
-    <row r="29" ht="20.1" customHeight="1" spans="3:13">
+    <row r="29" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C29" s="8">
         <v>10301</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="G29" s="8">
         <v>10302</v>
@@ -3942,24 +3085,24 @@
         <v>1500000</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" ht="20.1" customHeight="1" spans="3:238">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C30" s="8">
         <v>10302</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>106</v>
+        <v>209</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="G30" s="8">
         <v>10303</v>
@@ -3977,25 +3120,25 @@
         <v>2000000</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="ID30"/>
     </row>
-    <row r="31" ht="19.5" customHeight="1" spans="3:238">
+    <row r="31" spans="3:238" ht="19.5" customHeight="1">
       <c r="C31" s="8">
         <v>10303</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="G31" s="8">
         <v>10304</v>
@@ -4013,25 +3156,25 @@
         <v>2500000</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="ID31"/>
     </row>
-    <row r="32" ht="19.5" customHeight="1" spans="3:238">
+    <row r="32" spans="3:238" ht="19.5" customHeight="1">
       <c r="C32" s="8">
         <v>10304</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>112</v>
+        <v>209</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="G32" s="8">
         <v>10305</v>
@@ -4049,25 +3192,25 @@
         <v>3000000</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="ID32"/>
     </row>
-    <row r="33" ht="20.1" customHeight="1" spans="3:13">
+    <row r="33" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C33" s="8">
         <v>10305</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>115</v>
+        <v>209</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="G33" s="8">
         <v>10306</v>
@@ -4085,24 +3228,24 @@
         <v>4000000</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="34" ht="20.1" customHeight="1" spans="3:238">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C34" s="8">
         <v>10306</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>118</v>
+        <v>209</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="G34" s="8">
         <v>10307</v>
@@ -4120,25 +3263,25 @@
         <v>5000000</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M34" s="11" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="ID34"/>
     </row>
-    <row r="35" ht="19.5" customHeight="1" spans="3:238">
+    <row r="35" spans="3:238" ht="19.5" customHeight="1">
       <c r="C35" s="8">
         <v>10307</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="G35" s="8">
         <v>10308</v>
@@ -4156,25 +3299,25 @@
         <v>6000000</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="M35" s="11" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="ID35"/>
     </row>
-    <row r="36" ht="19.5" customHeight="1" spans="3:238">
+    <row r="36" spans="3:238" ht="19.5" customHeight="1">
       <c r="C36" s="8">
         <v>10308</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>124</v>
+        <v>209</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="G36" s="8">
         <v>10309</v>
@@ -4192,25 +3335,25 @@
         <v>7000000</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="M36" s="11" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="ID36"/>
     </row>
-    <row r="37" ht="19.5" customHeight="1" spans="3:238">
+    <row r="37" spans="3:238" ht="19.5" customHeight="1">
       <c r="C37" s="8">
         <v>10309</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>127</v>
+        <v>209</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="G37" s="8">
         <v>10310</v>
@@ -4228,25 +3371,25 @@
         <v>8000000</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M37" s="11" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="ID37"/>
     </row>
-    <row r="38" ht="19.5" customHeight="1" spans="3:238">
+    <row r="38" spans="3:238" ht="19.5" customHeight="1">
       <c r="C38" s="8">
         <v>10310</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="G38" s="8">
         <v>0</v>
@@ -4261,28 +3404,28 @@
         <v>126000</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="M38" s="11" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="ID38"/>
     </row>
-    <row r="39" ht="22.5" customHeight="1" spans="3:13">
+    <row r="39" spans="3:238" ht="22.5" customHeight="1">
       <c r="C39" s="8">
         <v>10400</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>133</v>
+        <v>210</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="G39" s="8">
         <v>10401</v>
@@ -4300,22 +3443,22 @@
         <v>1000000</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M39" s="11"/>
     </row>
-    <row r="40" ht="20.1" customHeight="1" spans="3:13">
+    <row r="40" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C40" s="8">
         <v>10401</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="G40" s="8">
         <v>10402</v>
@@ -4333,24 +3476,24 @@
         <v>1500000</v>
       </c>
       <c r="L40" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M40" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="41" ht="20.1" customHeight="1" spans="3:238">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C41" s="8">
         <v>10402</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="G41" s="8">
         <v>10403</v>
@@ -4368,25 +3511,25 @@
         <v>2000000</v>
       </c>
       <c r="L41" s="10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M41" s="11" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="ID41"/>
     </row>
-    <row r="42" ht="19.5" customHeight="1" spans="3:238">
+    <row r="42" spans="3:238" ht="19.5" customHeight="1">
       <c r="C42" s="8">
         <v>10403</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="G42" s="8">
         <v>10404</v>
@@ -4404,25 +3547,25 @@
         <v>2500000</v>
       </c>
       <c r="L42" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M42" s="11" t="s">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="ID42"/>
     </row>
-    <row r="43" ht="19.5" customHeight="1" spans="3:238">
+    <row r="43" spans="3:238" ht="19.5" customHeight="1">
       <c r="C43" s="8">
         <v>10404</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>145</v>
+        <v>210</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="G43" s="8">
         <v>10405</v>
@@ -4440,25 +3583,25 @@
         <v>3000000</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M43" s="11" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="ID43"/>
     </row>
-    <row r="44" ht="22.5" customHeight="1" spans="3:13">
+    <row r="44" spans="3:238" ht="22.5" customHeight="1">
       <c r="C44" s="8">
         <v>10405</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="G44" s="8">
         <v>10406</v>
@@ -4476,24 +3619,24 @@
         <v>4000000</v>
       </c>
       <c r="L44" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M44" s="11" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="45" ht="20.1" customHeight="1" spans="3:13">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C45" s="8">
         <v>10406</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>151</v>
+        <v>210</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="G45" s="8">
         <v>10407</v>
@@ -4511,24 +3654,24 @@
         <v>5000000</v>
       </c>
       <c r="L45" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M45" s="11" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="46" ht="20.1" customHeight="1" spans="3:238">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C46" s="8">
         <v>10407</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="G46" s="8">
         <v>10408</v>
@@ -4546,25 +3689,25 @@
         <v>6000000</v>
       </c>
       <c r="L46" s="10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="M46" s="11" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="ID46"/>
     </row>
-    <row r="47" ht="19.5" customHeight="1" spans="3:238">
+    <row r="47" spans="3:238" ht="19.5" customHeight="1">
       <c r="C47" s="8">
         <v>10408</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>157</v>
+        <v>210</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="G47" s="8">
         <v>10409</v>
@@ -4582,25 +3725,25 @@
         <v>7000000</v>
       </c>
       <c r="L47" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="M47" s="11" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="ID47"/>
     </row>
-    <row r="48" ht="19.5" customHeight="1" spans="3:238">
+    <row r="48" spans="3:238" ht="19.5" customHeight="1">
       <c r="C48" s="8">
         <v>10409</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="G48" s="8">
         <v>10410</v>
@@ -4618,25 +3761,25 @@
         <v>8000000</v>
       </c>
       <c r="L48" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M48" s="11" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="ID48"/>
     </row>
-    <row r="49" ht="19.5" customHeight="1" spans="3:238">
+    <row r="49" spans="3:238" ht="19.5" customHeight="1">
       <c r="C49" s="8">
         <v>10410</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="G49" s="8">
         <v>0</v>
@@ -4651,28 +3794,28 @@
         <v>126000</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="L49" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="M49" s="11" t="s">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="ID49"/>
     </row>
-    <row r="50" ht="22.5" customHeight="1" spans="3:13">
+    <row r="50" spans="3:238" ht="22.5" customHeight="1">
       <c r="C50" s="8">
         <v>10500</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>166</v>
+        <v>211</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G50" s="8">
         <v>10501</v>
@@ -4690,22 +3833,22 @@
         <v>1000000</v>
       </c>
       <c r="L50" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M50" s="11"/>
     </row>
-    <row r="51" ht="20.1" customHeight="1" spans="3:13">
+    <row r="51" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C51" s="8">
         <v>10501</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>168</v>
+        <v>123</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G51" s="8">
         <v>10502</v>
@@ -4723,24 +3866,24 @@
         <v>1500000</v>
       </c>
       <c r="L51" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M51" s="11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="52" ht="20.1" customHeight="1" spans="3:238">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="52" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C52" s="8">
         <v>10502</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G52" s="8">
         <v>10503</v>
@@ -4758,25 +3901,25 @@
         <v>2000000</v>
       </c>
       <c r="L52" s="10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M52" s="11" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="ID52"/>
     </row>
-    <row r="53" ht="19.5" customHeight="1" spans="3:238">
+    <row r="53" spans="3:238" ht="19.5" customHeight="1">
       <c r="C53" s="8">
         <v>10503</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G53" s="8">
         <v>10504</v>
@@ -4794,25 +3937,25 @@
         <v>2500000</v>
       </c>
       <c r="L53" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M53" s="11" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="ID53"/>
     </row>
-    <row r="54" ht="19.5" customHeight="1" spans="3:238">
+    <row r="54" spans="3:238" ht="19.5" customHeight="1">
       <c r="C54" s="8">
         <v>10504</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G54" s="8">
         <v>10505</v>
@@ -4830,25 +3973,25 @@
         <v>3000000</v>
       </c>
       <c r="L54" s="10" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M54" s="11" t="s">
-        <v>179</v>
+        <v>130</v>
       </c>
       <c r="ID54"/>
     </row>
-    <row r="55" ht="22.5" customHeight="1" spans="3:13">
+    <row r="55" spans="3:238" ht="22.5" customHeight="1">
       <c r="C55" s="8">
         <v>10505</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>180</v>
+        <v>131</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G55" s="8">
         <v>10506</v>
@@ -4866,24 +4009,24 @@
         <v>4000000</v>
       </c>
       <c r="L55" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M55" s="11" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="56" ht="20.1" customHeight="1" spans="3:13">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="56" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C56" s="8">
         <v>10506</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>183</v>
+        <v>133</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G56" s="8">
         <v>10507</v>
@@ -4901,24 +4044,24 @@
         <v>5000000</v>
       </c>
       <c r="L56" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M56" s="11" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="57" ht="20.1" customHeight="1" spans="3:238">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="57" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C57" s="8">
         <v>10507</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>186</v>
+        <v>135</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G57" s="8">
         <v>10508</v>
@@ -4936,25 +4079,25 @@
         <v>6000000</v>
       </c>
       <c r="L57" s="10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="M57" s="11" t="s">
-        <v>188</v>
+        <v>136</v>
       </c>
       <c r="ID57"/>
     </row>
-    <row r="58" ht="19.5" customHeight="1" spans="3:238">
+    <row r="58" spans="3:238" ht="19.5" customHeight="1">
       <c r="C58" s="8">
         <v>10508</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>189</v>
+        <v>137</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G58" s="8">
         <v>10509</v>
@@ -4972,25 +4115,25 @@
         <v>7000000</v>
       </c>
       <c r="L58" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="M58" s="11" t="s">
-        <v>191</v>
+        <v>138</v>
       </c>
       <c r="ID58"/>
     </row>
-    <row r="59" ht="19.5" customHeight="1" spans="3:238">
+    <row r="59" spans="3:238" ht="19.5" customHeight="1">
       <c r="C59" s="8">
         <v>10509</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G59" s="8">
         <v>10510</v>
@@ -5008,25 +4151,25 @@
         <v>8000000</v>
       </c>
       <c r="L59" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M59" s="11" t="s">
-        <v>194</v>
+        <v>140</v>
       </c>
       <c r="ID59"/>
     </row>
-    <row r="60" ht="19.5" customHeight="1" spans="3:238">
+    <row r="60" spans="3:238" ht="19.5" customHeight="1">
       <c r="C60" s="8">
         <v>10510</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>195</v>
+        <v>141</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G60" s="8">
         <v>0</v>
@@ -5041,28 +4184,28 @@
         <v>126000</v>
       </c>
       <c r="K60" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="L60" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="M60" s="11" t="s">
-        <v>197</v>
+        <v>142</v>
       </c>
       <c r="ID60"/>
     </row>
-    <row r="61" ht="22.5" customHeight="1" spans="3:13">
+    <row r="61" spans="3:238" ht="22.5" customHeight="1">
       <c r="C61" s="8">
         <v>10600</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>198</v>
+        <v>143</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="G61" s="8">
         <v>10601</v>
@@ -5080,22 +4223,22 @@
         <v>1000000</v>
       </c>
       <c r="L61" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M61" s="11"/>
     </row>
-    <row r="62" ht="20.1" customHeight="1" spans="3:13">
+    <row r="62" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C62" s="8">
         <v>10601</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>201</v>
+        <v>145</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="G62" s="8">
         <v>10602</v>
@@ -5113,24 +4256,24 @@
         <v>1500000</v>
       </c>
       <c r="L62" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M62" s="11" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="63" ht="20.1" customHeight="1" spans="3:238">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C63" s="8">
         <v>10602</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>204</v>
+        <v>147</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="G63" s="8">
         <v>10603</v>
@@ -5148,25 +4291,25 @@
         <v>2000000</v>
       </c>
       <c r="L63" s="10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M63" s="11" t="s">
-        <v>206</v>
+        <v>148</v>
       </c>
       <c r="ID63"/>
     </row>
-    <row r="64" ht="19.5" customHeight="1" spans="3:238">
+    <row r="64" spans="3:238" ht="19.5" customHeight="1">
       <c r="C64" s="8">
         <v>10603</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="G64" s="8">
         <v>10604</v>
@@ -5184,25 +4327,25 @@
         <v>2500000</v>
       </c>
       <c r="L64" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M64" s="11" t="s">
-        <v>209</v>
+        <v>150</v>
       </c>
       <c r="ID64"/>
     </row>
-    <row r="65" ht="19.5" customHeight="1" spans="3:238">
+    <row r="65" spans="3:238" ht="19.5" customHeight="1">
       <c r="C65" s="8">
         <v>10604</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>210</v>
+        <v>151</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="G65" s="8">
         <v>10605</v>
@@ -5220,25 +4363,25 @@
         <v>3000000</v>
       </c>
       <c r="L65" s="10" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M65" s="11" t="s">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="ID65"/>
     </row>
-    <row r="66" ht="22.5" customHeight="1" spans="3:13">
+    <row r="66" spans="3:238" ht="22.5" customHeight="1">
       <c r="C66" s="8">
         <v>10605</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>213</v>
+        <v>153</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="G66" s="8">
         <v>10606</v>
@@ -5256,24 +4399,24 @@
         <v>4000000</v>
       </c>
       <c r="L66" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M66" s="11" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="67" ht="20.1" customHeight="1" spans="3:13">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="67" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C67" s="8">
         <v>10606</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>216</v>
+        <v>155</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="G67" s="8">
         <v>10607</v>
@@ -5291,24 +4434,24 @@
         <v>5000000</v>
       </c>
       <c r="L67" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M67" s="11" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="68" ht="20.1" customHeight="1" spans="3:238">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="68" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C68" s="8">
         <v>10607</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>219</v>
+        <v>157</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="G68" s="8">
         <v>10608</v>
@@ -5326,25 +4469,25 @@
         <v>6000000</v>
       </c>
       <c r="L68" s="10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="M68" s="11" t="s">
-        <v>221</v>
+        <v>158</v>
       </c>
       <c r="ID68"/>
     </row>
-    <row r="69" ht="19.5" customHeight="1" spans="3:238">
+    <row r="69" spans="3:238" ht="19.5" customHeight="1">
       <c r="C69" s="8">
         <v>10608</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>222</v>
+        <v>159</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="G69" s="8">
         <v>10609</v>
@@ -5362,25 +4505,25 @@
         <v>7000000</v>
       </c>
       <c r="L69" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="M69" s="11" t="s">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="ID69"/>
     </row>
-    <row r="70" ht="19.5" customHeight="1" spans="3:238">
+    <row r="70" spans="3:238" ht="19.5" customHeight="1">
       <c r="C70" s="8">
         <v>10609</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="G70" s="8">
         <v>10610</v>
@@ -5398,25 +4541,25 @@
         <v>8000000</v>
       </c>
       <c r="L70" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M70" s="11" t="s">
-        <v>227</v>
+        <v>162</v>
       </c>
       <c r="ID70"/>
     </row>
-    <row r="71" ht="19.5" customHeight="1" spans="3:238">
+    <row r="71" spans="3:238" ht="19.5" customHeight="1">
       <c r="C71" s="8">
         <v>10610</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>228</v>
+        <v>163</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="G71" s="8">
         <v>0</v>
@@ -5431,28 +4574,28 @@
         <v>126000</v>
       </c>
       <c r="K71" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="L71" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="M71" s="11" t="s">
-        <v>230</v>
+        <v>164</v>
       </c>
       <c r="ID71"/>
     </row>
-    <row r="72" ht="22.5" customHeight="1" spans="3:13">
+    <row r="72" spans="3:238" ht="22.5" customHeight="1">
       <c r="C72" s="8">
         <v>10700</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="G72" s="8">
         <v>10701</v>
@@ -5470,22 +4613,22 @@
         <v>1000000</v>
       </c>
       <c r="L72" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M72" s="11"/>
     </row>
-    <row r="73" ht="20.1" customHeight="1" spans="3:13">
+    <row r="73" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C73" s="8">
         <v>10701</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>234</v>
+        <v>167</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="G73" s="8">
         <v>10702</v>
@@ -5503,24 +4646,24 @@
         <v>1500000</v>
       </c>
       <c r="L73" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M73" s="11" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="74" ht="20.1" customHeight="1" spans="3:238">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="74" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C74" s="8">
         <v>10702</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>237</v>
+        <v>169</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="G74" s="8">
         <v>10703</v>
@@ -5538,25 +4681,25 @@
         <v>2000000</v>
       </c>
       <c r="L74" s="10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M74" s="11" t="s">
-        <v>239</v>
+        <v>170</v>
       </c>
       <c r="ID74"/>
     </row>
-    <row r="75" ht="19.5" customHeight="1" spans="3:238">
+    <row r="75" spans="3:238" ht="19.5" customHeight="1">
       <c r="C75" s="8">
         <v>10703</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>240</v>
+        <v>171</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="G75" s="8">
         <v>10704</v>
@@ -5574,25 +4717,25 @@
         <v>2500000</v>
       </c>
       <c r="L75" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M75" s="11" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="ID75"/>
     </row>
-    <row r="76" ht="19.5" customHeight="1" spans="3:238">
+    <row r="76" spans="3:238" ht="19.5" customHeight="1">
       <c r="C76" s="8">
         <v>10704</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="G76" s="8">
         <v>10705</v>
@@ -5610,25 +4753,25 @@
         <v>3000000</v>
       </c>
       <c r="L76" s="10" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M76" s="11" t="s">
-        <v>245</v>
+        <v>174</v>
       </c>
       <c r="ID76"/>
     </row>
-    <row r="77" ht="22.5" customHeight="1" spans="3:13">
+    <row r="77" spans="3:238" ht="22.5" customHeight="1">
       <c r="C77" s="8">
         <v>10705</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>246</v>
+        <v>175</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="G77" s="8">
         <v>10706</v>
@@ -5646,24 +4789,24 @@
         <v>4000000</v>
       </c>
       <c r="L77" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M77" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="78" ht="20.1" customHeight="1" spans="3:13">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="78" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C78" s="8">
         <v>10706</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>249</v>
+        <v>177</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="G78" s="8">
         <v>10707</v>
@@ -5681,24 +4824,24 @@
         <v>5000000</v>
       </c>
       <c r="L78" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M78" s="11" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="79" ht="20.1" customHeight="1" spans="3:238">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="79" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C79" s="8">
         <v>10707</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>252</v>
+        <v>179</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="G79" s="8">
         <v>10708</v>
@@ -5716,25 +4859,25 @@
         <v>6000000</v>
       </c>
       <c r="L79" s="10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="M79" s="11" t="s">
-        <v>254</v>
+        <v>180</v>
       </c>
       <c r="ID79"/>
     </row>
-    <row r="80" ht="19.5" customHeight="1" spans="3:238">
+    <row r="80" spans="3:238" ht="19.5" customHeight="1">
       <c r="C80" s="8">
         <v>10708</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>255</v>
+        <v>181</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>256</v>
+        <v>213</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="G80" s="8">
         <v>10709</v>
@@ -5752,25 +4895,25 @@
         <v>7000000</v>
       </c>
       <c r="L80" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="M80" s="11" t="s">
-        <v>257</v>
+        <v>182</v>
       </c>
       <c r="ID80"/>
     </row>
-    <row r="81" ht="19.5" customHeight="1" spans="3:238">
+    <row r="81" spans="3:238" ht="19.5" customHeight="1">
       <c r="C81" s="8">
         <v>10709</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>258</v>
+        <v>183</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>259</v>
+        <v>213</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="G81" s="8">
         <v>10710</v>
@@ -5788,25 +4931,25 @@
         <v>8000000</v>
       </c>
       <c r="L81" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M81" s="11" t="s">
-        <v>260</v>
+        <v>184</v>
       </c>
       <c r="ID81"/>
     </row>
-    <row r="82" ht="19.5" customHeight="1" spans="3:238">
+    <row r="82" spans="3:238" ht="19.5" customHeight="1">
       <c r="C82" s="8">
         <v>10710</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>261</v>
+        <v>185</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>262</v>
+        <v>213</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="G82" s="8">
         <v>0</v>
@@ -5821,28 +4964,28 @@
         <v>126000</v>
       </c>
       <c r="K82" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="L82" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="M82" s="11" t="s">
-        <v>263</v>
+        <v>186</v>
       </c>
       <c r="ID82"/>
     </row>
-    <row r="83" ht="22.5" customHeight="1" spans="3:13">
+    <row r="83" spans="3:238" ht="22.5" customHeight="1">
       <c r="C83" s="8">
         <v>10800</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>264</v>
+        <v>187</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>265</v>
+        <v>214</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="G83" s="8">
         <v>10801</v>
@@ -5860,22 +5003,22 @@
         <v>1000000</v>
       </c>
       <c r="L83" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M83" s="11"/>
     </row>
-    <row r="84" ht="20.1" customHeight="1" spans="3:13">
+    <row r="84" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C84" s="8">
         <v>10801</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>267</v>
+        <v>189</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>268</v>
+        <v>214</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="G84" s="8">
         <v>10802</v>
@@ -5893,24 +5036,24 @@
         <v>1500000</v>
       </c>
       <c r="L84" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M84" s="11" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="85" ht="20.1" customHeight="1" spans="3:238">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="85" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C85" s="8">
         <v>10802</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>270</v>
+        <v>191</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>271</v>
+        <v>214</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="G85" s="8">
         <v>10803</v>
@@ -5928,25 +5071,25 @@
         <v>2000000</v>
       </c>
       <c r="L85" s="10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M85" s="11" t="s">
-        <v>272</v>
+        <v>192</v>
       </c>
       <c r="ID85"/>
     </row>
-    <row r="86" ht="19.5" customHeight="1" spans="3:238">
+    <row r="86" spans="3:238" ht="19.5" customHeight="1">
       <c r="C86" s="8">
         <v>10803</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>273</v>
+        <v>193</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>274</v>
+        <v>214</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="G86" s="8">
         <v>10804</v>
@@ -5964,25 +5107,25 @@
         <v>2500000</v>
       </c>
       <c r="L86" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M86" s="11" t="s">
-        <v>275</v>
+        <v>194</v>
       </c>
       <c r="ID86"/>
     </row>
-    <row r="87" ht="19.5" customHeight="1" spans="3:238">
+    <row r="87" spans="3:238" ht="19.5" customHeight="1">
       <c r="C87" s="8">
         <v>10804</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>276</v>
+        <v>195</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>277</v>
+        <v>214</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="G87" s="8">
         <v>10805</v>
@@ -6000,25 +5143,25 @@
         <v>3000000</v>
       </c>
       <c r="L87" s="10" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M87" s="11" t="s">
-        <v>278</v>
+        <v>196</v>
       </c>
       <c r="ID87"/>
     </row>
-    <row r="88" ht="22.5" customHeight="1" spans="3:13">
+    <row r="88" spans="3:238" ht="22.5" customHeight="1">
       <c r="C88" s="8">
         <v>10805</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>279</v>
+        <v>197</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>280</v>
+        <v>214</v>
       </c>
       <c r="F88" s="10" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="G88" s="8">
         <v>10806</v>
@@ -6036,24 +5179,24 @@
         <v>4000000</v>
       </c>
       <c r="L88" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M88" s="11" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="89" ht="20.1" customHeight="1" spans="3:13">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="89" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C89" s="8">
         <v>10806</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>282</v>
+        <v>199</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>283</v>
+        <v>214</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="G89" s="8">
         <v>10807</v>
@@ -6071,24 +5214,24 @@
         <v>5000000</v>
       </c>
       <c r="L89" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M89" s="11" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="90" ht="20.1" customHeight="1" spans="3:238">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="90" spans="3:238" ht="20.100000000000001" customHeight="1">
       <c r="C90" s="8">
         <v>10807</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>285</v>
+        <v>201</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>286</v>
+        <v>214</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="G90" s="8">
         <v>10808</v>
@@ -6106,25 +5249,25 @@
         <v>6000000</v>
       </c>
       <c r="L90" s="10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="M90" s="11" t="s">
-        <v>287</v>
+        <v>202</v>
       </c>
       <c r="ID90"/>
     </row>
-    <row r="91" ht="19.5" customHeight="1" spans="3:238">
+    <row r="91" spans="3:238" ht="19.5" customHeight="1">
       <c r="C91" s="8">
         <v>10808</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>288</v>
+        <v>203</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>289</v>
+        <v>214</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="G91" s="8">
         <v>10809</v>
@@ -6142,25 +5285,25 @@
         <v>7000000</v>
       </c>
       <c r="L91" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="M91" s="11" t="s">
-        <v>290</v>
+        <v>204</v>
       </c>
       <c r="ID91"/>
     </row>
-    <row r="92" ht="19.5" customHeight="1" spans="3:238">
+    <row r="92" spans="3:238" ht="19.5" customHeight="1">
       <c r="C92" s="8">
         <v>10809</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>291</v>
+        <v>205</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>292</v>
+        <v>214</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="G92" s="8">
         <v>10810</v>
@@ -6178,25 +5321,25 @@
         <v>8000000</v>
       </c>
       <c r="L92" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M92" s="11" t="s">
-        <v>293</v>
+        <v>206</v>
       </c>
       <c r="ID92"/>
     </row>
-    <row r="93" ht="19.5" customHeight="1" spans="3:238">
+    <row r="93" spans="3:238" ht="19.5" customHeight="1">
       <c r="C93" s="8">
         <v>10810</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>294</v>
+        <v>207</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>295</v>
+        <v>214</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="G93" s="8">
         <v>0</v>
@@ -6211,22 +5354,23 @@
         <v>126000</v>
       </c>
       <c r="K93" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="L93" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="M93" s="11" t="s">
-        <v>296</v>
+        <v>208</v>
       </c>
       <c r="ID93"/>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/UnionKeJiConfig.xlsx
+++ b/Excel/UnionKeJiConfig.xlsx
@@ -1,38 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC235C6-32C3-44E2-ABF6-1C5900711B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="UnionKeJiProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="M3" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>作者:
 10.生命值
@@ -89,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="137">
   <si>
     <t>Id</t>
   </si>
@@ -157,7 +164,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>经验科技0级</t>
+    <t>经验科技</t>
+  </si>
+  <si>
+    <t>Experience</t>
   </si>
   <si>
     <t>keji_1</t>
@@ -166,595 +176,350 @@
     <t>16;500@10000163;10</t>
   </si>
   <si>
-    <t>经验科技1级</t>
-  </si>
-  <si>
     <t>16;750@10000163;15</t>
   </si>
   <si>
     <t>220103;0.01</t>
   </si>
   <si>
-    <t>经验科技2级</t>
-  </si>
-  <si>
     <t>16;1000@10000163;20</t>
   </si>
   <si>
     <t>220103;0.02</t>
   </si>
   <si>
-    <t>经验科技3级</t>
-  </si>
-  <si>
     <t>16;1300@10000163;25</t>
   </si>
   <si>
     <t>220103;0.03</t>
   </si>
   <si>
-    <t>经验科技4级</t>
-  </si>
-  <si>
     <t>16;1600@10000163;30</t>
   </si>
   <si>
     <t>220103;0.04</t>
   </si>
   <si>
-    <t>经验科技5级</t>
-  </si>
-  <si>
     <t>16;2000@10000163;35</t>
   </si>
   <si>
     <t>220103;0.05</t>
   </si>
   <si>
-    <t>经验科技6级</t>
-  </si>
-  <si>
     <t>16;2400@10000163;40</t>
   </si>
   <si>
     <t>220103;0.06</t>
   </si>
   <si>
-    <t>经验科技7级</t>
-  </si>
-  <si>
     <t>16;2800@10000163;45</t>
   </si>
   <si>
     <t>220103;0.07</t>
   </si>
   <si>
-    <t>经验科技8级</t>
-  </si>
-  <si>
     <t>16;3200@10000163;50</t>
   </si>
   <si>
     <t>220103;0.08</t>
   </si>
   <si>
-    <t>经验科技9级</t>
-  </si>
-  <si>
     <t>16;3600@10000163;60</t>
   </si>
   <si>
     <t>220103;0.09</t>
   </si>
   <si>
-    <t>经验科技10级</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
     <t>220103;0.10</t>
   </si>
   <si>
-    <t>金币科技0级</t>
+    <t>金币科技</t>
+  </si>
+  <si>
+    <t>Gold</t>
   </si>
   <si>
     <t>keji_2</t>
   </si>
   <si>
-    <t>金币科技1级</t>
-  </si>
-  <si>
     <t>220203;0.01</t>
   </si>
   <si>
-    <t>金币科技2级</t>
-  </si>
-  <si>
     <t>220203;0.02</t>
   </si>
   <si>
-    <t>金币科技3级</t>
-  </si>
-  <si>
     <t>220203;0.03</t>
   </si>
   <si>
-    <t>金币科技4级</t>
-  </si>
-  <si>
     <t>220203;0.04</t>
   </si>
   <si>
-    <t>金币科技5级</t>
-  </si>
-  <si>
     <t>220203;0.05</t>
   </si>
   <si>
-    <t>金币科技6级</t>
-  </si>
-  <si>
     <t>220203;0.06</t>
   </si>
   <si>
-    <t>金币科技7级</t>
-  </si>
-  <si>
     <t>220203;0.07</t>
   </si>
   <si>
-    <t>金币科技8级</t>
-  </si>
-  <si>
     <t>220203;0.08</t>
   </si>
   <si>
-    <t>金币科技9级</t>
-  </si>
-  <si>
     <t>220203;0.09</t>
   </si>
   <si>
-    <t>金币科技10级</t>
-  </si>
-  <si>
     <t>220203;0.10</t>
   </si>
   <si>
-    <t>怪之攻伤0级</t>
+    <t>怪之攻伤</t>
+  </si>
+  <si>
+    <t>Monster Damage</t>
   </si>
   <si>
     <t>keji_3</t>
   </si>
   <si>
-    <t>怪之攻伤1级</t>
-  </si>
-  <si>
     <t>223003;0.01</t>
   </si>
   <si>
-    <t>怪之攻伤2级</t>
-  </si>
-  <si>
     <t>223003;0.02</t>
   </si>
   <si>
-    <t>怪之攻伤3级</t>
-  </si>
-  <si>
     <t>223003;0.03</t>
   </si>
   <si>
-    <t>怪之攻伤4级</t>
-  </si>
-  <si>
     <t>223003;0.04</t>
   </si>
   <si>
-    <t>怪之攻伤5级</t>
-  </si>
-  <si>
     <t>223003;0.05</t>
   </si>
   <si>
-    <t>怪之攻伤6级</t>
-  </si>
-  <si>
     <t>223003;0.06</t>
   </si>
   <si>
-    <t>怪之攻伤7级</t>
-  </si>
-  <si>
     <t>223003;0.07</t>
   </si>
   <si>
-    <t>怪之攻伤8级</t>
-  </si>
-  <si>
     <t>223003;0.08</t>
   </si>
   <si>
-    <t>怪之攻伤9级</t>
-  </si>
-  <si>
     <t>223003;0.09</t>
   </si>
   <si>
-    <t>怪之攻伤10级</t>
-  </si>
-  <si>
     <t>223003;0.10</t>
   </si>
   <si>
-    <t>怪之技伤0级</t>
+    <t>怪之技伤</t>
+  </si>
+  <si>
+    <t>Monster Skill</t>
   </si>
   <si>
     <t>keji_4</t>
   </si>
   <si>
-    <t>怪之技伤1级</t>
-  </si>
-  <si>
     <t>223103;0.01</t>
   </si>
   <si>
-    <t>怪之技伤2级</t>
-  </si>
-  <si>
     <t>223103;0.02</t>
   </si>
   <si>
-    <t>怪之技伤3级</t>
-  </si>
-  <si>
     <t>223103;0.03</t>
   </si>
   <si>
-    <t>怪之技伤4级</t>
-  </si>
-  <si>
     <t>223103;0.04</t>
   </si>
   <si>
-    <t>怪之技伤5级</t>
-  </si>
-  <si>
     <t>223103;0.05</t>
   </si>
   <si>
-    <t>怪之技伤6级</t>
-  </si>
-  <si>
     <t>223103;0.06</t>
   </si>
   <si>
-    <t>怪之技伤7级</t>
-  </si>
-  <si>
     <t>223103;0.07</t>
   </si>
   <si>
-    <t>怪之技伤8级</t>
-  </si>
-  <si>
     <t>223103;0.08</t>
   </si>
   <si>
-    <t>怪之技伤9级</t>
-  </si>
-  <si>
     <t>223103;0.09</t>
   </si>
   <si>
-    <t>怪之技伤10级</t>
-  </si>
-  <si>
     <t>223103;0.10</t>
   </si>
   <si>
-    <t>怪之攻防0级</t>
+    <t>怪之攻防</t>
+  </si>
+  <si>
+    <t>Monster Defence</t>
   </si>
   <si>
     <t>keji_5</t>
   </si>
   <si>
-    <t>怪之攻防1级</t>
-  </si>
-  <si>
     <t>223203;0.01</t>
   </si>
   <si>
-    <t>怪之攻防2级</t>
-  </si>
-  <si>
     <t>223203;0.02</t>
   </si>
   <si>
-    <t>怪之攻防3级</t>
-  </si>
-  <si>
     <t>223203;0.03</t>
   </si>
   <si>
-    <t>怪之攻防4级</t>
-  </si>
-  <si>
     <t>223203;0.04</t>
   </si>
   <si>
-    <t>怪之攻防5级</t>
-  </si>
-  <si>
     <t>223203;0.05</t>
   </si>
   <si>
-    <t>怪之攻防6级</t>
-  </si>
-  <si>
     <t>223203;0.06</t>
   </si>
   <si>
-    <t>怪之攻防7级</t>
-  </si>
-  <si>
     <t>223203;0.07</t>
   </si>
   <si>
-    <t>怪之攻防8级</t>
-  </si>
-  <si>
     <t>223203;0.08</t>
   </si>
   <si>
-    <t>怪之攻防9级</t>
-  </si>
-  <si>
     <t>223203;0.09</t>
   </si>
   <si>
-    <t>怪之攻防10级</t>
-  </si>
-  <si>
     <t>223203;0.10</t>
   </si>
   <si>
-    <t>怪之技防0级</t>
+    <t>怪之技防</t>
+  </si>
+  <si>
+    <t>Monster Arts Defence</t>
   </si>
   <si>
     <t>keji_6</t>
   </si>
   <si>
-    <t>怪之技防1级</t>
-  </si>
-  <si>
     <t>223303;0.01</t>
   </si>
   <si>
-    <t>怪之技防2级</t>
-  </si>
-  <si>
     <t>223303;0.02</t>
   </si>
   <si>
-    <t>怪之技防3级</t>
-  </si>
-  <si>
     <t>223303;0.03</t>
   </si>
   <si>
-    <t>怪之技防4级</t>
-  </si>
-  <si>
     <t>223303;0.04</t>
   </si>
   <si>
-    <t>怪之技防5级</t>
-  </si>
-  <si>
     <t>223303;0.05</t>
   </si>
   <si>
-    <t>怪之技防6级</t>
-  </si>
-  <si>
     <t>223303;0.06</t>
   </si>
   <si>
-    <t>怪之技防7级</t>
-  </si>
-  <si>
     <t>223303;0.07</t>
   </si>
   <si>
-    <t>怪之技防8级</t>
-  </si>
-  <si>
     <t>223303;0.08</t>
   </si>
   <si>
-    <t>怪之技防9级</t>
-  </si>
-  <si>
     <t>223303;0.09</t>
   </si>
   <si>
-    <t>怪之技防10级</t>
-  </si>
-  <si>
     <t>223303;0.10</t>
   </si>
   <si>
-    <t>玩家攻减0级</t>
+    <t>玩家攻减</t>
+  </si>
+  <si>
+    <t>Player Defence</t>
   </si>
   <si>
     <t>keji_7</t>
   </si>
   <si>
-    <t>玩家攻减1级</t>
-  </si>
-  <si>
     <t>205703;0.01</t>
   </si>
   <si>
-    <t>玩家攻减2级</t>
-  </si>
-  <si>
     <t>205703;0.02</t>
   </si>
   <si>
-    <t>玩家攻减3级</t>
-  </si>
-  <si>
     <t>205703;0.03</t>
   </si>
   <si>
-    <t>玩家攻减4级</t>
-  </si>
-  <si>
     <t>205703;0.04</t>
   </si>
   <si>
-    <t>玩家攻减5级</t>
-  </si>
-  <si>
     <t>205703;0.05</t>
   </si>
   <si>
-    <t>玩家攻减6级</t>
-  </si>
-  <si>
     <t>205703;0.06</t>
   </si>
   <si>
-    <t>玩家攻减7级</t>
-  </si>
-  <si>
     <t>205703;0.07</t>
   </si>
   <si>
-    <t>玩家攻减8级</t>
-  </si>
-  <si>
     <t>205703;0.08</t>
   </si>
   <si>
-    <t>玩家攻减9级</t>
-  </si>
-  <si>
     <t>205703;0.09</t>
   </si>
   <si>
-    <t>玩家攻减10级</t>
-  </si>
-  <si>
     <t>205703;0.10</t>
   </si>
   <si>
-    <t>玩家技减0级</t>
+    <t>玩家技减</t>
+  </si>
+  <si>
+    <t>Player Arts Defence</t>
   </si>
   <si>
     <t>keji_8</t>
   </si>
   <si>
-    <t>玩家技减1级</t>
-  </si>
-  <si>
     <t>205803;0.01</t>
   </si>
   <si>
-    <t>玩家技减2级</t>
-  </si>
-  <si>
     <t>205803;0.02</t>
   </si>
   <si>
-    <t>玩家技减3级</t>
-  </si>
-  <si>
     <t>205803;0.03</t>
   </si>
   <si>
-    <t>玩家技减4级</t>
-  </si>
-  <si>
     <t>205803;0.04</t>
   </si>
   <si>
-    <t>玩家技减5级</t>
-  </si>
-  <si>
     <t>205803;0.05</t>
   </si>
   <si>
-    <t>玩家技减6级</t>
-  </si>
-  <si>
     <t>205803;0.06</t>
   </si>
   <si>
-    <t>玩家技减7级</t>
-  </si>
-  <si>
     <t>205803;0.07</t>
   </si>
   <si>
-    <t>玩家技减8级</t>
-  </si>
-  <si>
     <t>205803;0.08</t>
   </si>
   <si>
-    <t>玩家技减9级</t>
-  </si>
-  <si>
     <t>205803;0.09</t>
   </si>
   <si>
-    <t>玩家技减10级</t>
-  </si>
-  <si>
     <t>205803;0.10</t>
-  </si>
-  <si>
-    <t>Monster Damage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monster Skill</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monster Defence</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monster Arts Defence</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Player Defence</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Player Arts Defence</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gold</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -765,14 +530,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -780,37 +543,179 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -835,8 +740,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -930,9 +1021,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -962,10 +1295,57 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
@@ -1038,9 +1418,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2111,12 +2488,12 @@
       </a:style>
     </a:txDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="C1:ID93"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
@@ -2132,12 +2509,12 @@
     <col min="14" max="238" width="8.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:238" s="1" customFormat="1" ht="14.25"/>
-    <row r="2" spans="3:238" ht="13.5" customHeight="1">
+    <row r="1" s="1" customFormat="1" ht="14.25"/>
+    <row r="2" customHeight="1" spans="4:5">
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="3" ht="20.1" customHeight="1" spans="3:13">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -2172,7 +2549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="4" ht="20.1" customHeight="1" spans="3:13">
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -2207,7 +2584,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="5" ht="20.1" customHeight="1" spans="3:13">
       <c r="C5" s="4" t="s">
         <v>20</v>
       </c>
@@ -2242,7 +2619,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="6" ht="20.1" customHeight="1" spans="3:13">
       <c r="C6" s="8">
         <v>10100</v>
       </c>
@@ -2250,10 +2627,10 @@
         <v>22</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6" s="8">
         <v>10101</v>
@@ -2271,22 +2648,22 @@
         <v>1000000</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M6" s="11"/>
     </row>
-    <row r="7" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="7" ht="20.1" customHeight="1" spans="3:13">
       <c r="C7" s="8">
         <v>10101</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7" s="8">
         <v>10102</v>
@@ -2310,18 +2687,18 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="8" ht="20.1" customHeight="1" spans="3:238">
       <c r="C8" s="8">
         <v>10102</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G8" s="8">
         <v>10103</v>
@@ -2339,25 +2716,25 @@
         <v>2000000</v>
       </c>
       <c r="L8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="M8" s="11" t="s">
-        <v>30</v>
-      </c>
       <c r="ID8"/>
     </row>
-    <row r="9" spans="3:238" ht="19.5" customHeight="1">
+    <row r="9" ht="19.5" customHeight="1" spans="3:238">
       <c r="C9" s="8">
         <v>10103</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G9" s="8">
         <v>10104</v>
@@ -2375,25 +2752,25 @@
         <v>2500000</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="ID9"/>
     </row>
-    <row r="10" spans="3:238" ht="19.5" customHeight="1">
+    <row r="10" ht="19.5" customHeight="1" spans="3:238">
       <c r="C10" s="8">
         <v>10104</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G10" s="8">
         <v>10105</v>
@@ -2411,25 +2788,25 @@
         <v>3000000</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="ID10"/>
     </row>
-    <row r="11" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="11" ht="20.1" customHeight="1" spans="3:13">
       <c r="C11" s="8">
         <v>10105</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G11" s="8">
         <v>10106</v>
@@ -2447,24 +2824,24 @@
         <v>4000000</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" ht="20.1" customHeight="1" spans="3:238">
       <c r="C12" s="8">
         <v>10106</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G12" s="8">
         <v>10107</v>
@@ -2482,25 +2859,25 @@
         <v>5000000</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="ID12"/>
     </row>
-    <row r="13" spans="3:238" ht="19.5" customHeight="1">
+    <row r="13" ht="19.5" customHeight="1" spans="3:238">
       <c r="C13" s="8">
         <v>10107</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G13" s="8">
         <v>10108</v>
@@ -2518,25 +2895,25 @@
         <v>6000000</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="ID13"/>
     </row>
-    <row r="14" spans="3:238" ht="19.5" customHeight="1">
+    <row r="14" ht="19.5" customHeight="1" spans="3:238">
       <c r="C14" s="8">
         <v>10108</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G14" s="8">
         <v>10109</v>
@@ -2554,25 +2931,25 @@
         <v>7000000</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="ID14"/>
     </row>
-    <row r="15" spans="3:238" ht="19.5" customHeight="1">
+    <row r="15" ht="19.5" customHeight="1" spans="3:238">
       <c r="C15" s="8">
         <v>10109</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G15" s="8">
         <v>10110</v>
@@ -2590,25 +2967,25 @@
         <v>8000000</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="ID15"/>
     </row>
-    <row r="16" spans="3:238" ht="19.5" customHeight="1">
+    <row r="16" ht="19.5" customHeight="1" spans="3:238">
       <c r="C16" s="8">
         <v>10110</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G16" s="8">
         <v>0</v>
@@ -2623,28 +3000,28 @@
         <v>126000</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="ID16"/>
     </row>
-    <row r="17" spans="3:238" ht="22.5" customHeight="1">
+    <row r="17" ht="22.5" customHeight="1" spans="3:13">
       <c r="C17" s="8">
         <v>10200</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>216</v>
+        <v>47</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G17" s="8">
         <v>10201</v>
@@ -2662,22 +3039,22 @@
         <v>1000000</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M17" s="11"/>
     </row>
-    <row r="18" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="18" ht="20.1" customHeight="1" spans="3:13">
       <c r="C18" s="8">
         <v>10201</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>216</v>
+        <v>47</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G18" s="8">
         <v>10202</v>
@@ -2698,21 +3075,21 @@
         <v>26</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" spans="3:238">
       <c r="C19" s="8">
         <v>10202</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>216</v>
+        <v>47</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G19" s="8">
         <v>10203</v>
@@ -2730,25 +3107,25 @@
         <v>2000000</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="ID19"/>
     </row>
-    <row r="20" spans="3:238" ht="19.5" customHeight="1">
+    <row r="20" ht="19.5" customHeight="1" spans="3:238">
       <c r="C20" s="8">
         <v>10203</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>216</v>
+        <v>47</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G20" s="8">
         <v>10204</v>
@@ -2766,25 +3143,25 @@
         <v>2500000</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="ID20"/>
     </row>
-    <row r="21" spans="3:238" ht="19.5" customHeight="1">
+    <row r="21" ht="19.5" customHeight="1" spans="3:238">
       <c r="C21" s="8">
         <v>10204</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>216</v>
+        <v>47</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G21" s="8">
         <v>10205</v>
@@ -2802,25 +3179,25 @@
         <v>3000000</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="ID21"/>
     </row>
-    <row r="22" spans="3:238" ht="22.5" customHeight="1">
+    <row r="22" ht="22.5" customHeight="1" spans="3:13">
       <c r="C22" s="8">
         <v>10205</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>216</v>
+        <v>47</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G22" s="8">
         <v>10206</v>
@@ -2838,24 +3215,24 @@
         <v>4000000</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" spans="3:13">
       <c r="C23" s="8">
         <v>10206</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>216</v>
+        <v>47</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G23" s="8">
         <v>10207</v>
@@ -2873,24 +3250,24 @@
         <v>5000000</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" ht="20.1" customHeight="1" spans="3:238">
       <c r="C24" s="8">
         <v>10207</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>216</v>
+        <v>47</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G24" s="8">
         <v>10208</v>
@@ -2908,25 +3285,25 @@
         <v>6000000</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="ID24"/>
     </row>
-    <row r="25" spans="3:238" ht="19.5" customHeight="1">
+    <row r="25" ht="19.5" customHeight="1" spans="3:238">
       <c r="C25" s="8">
         <v>10208</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>216</v>
+        <v>47</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G25" s="8">
         <v>10209</v>
@@ -2944,25 +3321,25 @@
         <v>7000000</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="ID25"/>
     </row>
-    <row r="26" spans="3:238" ht="19.5" customHeight="1">
+    <row r="26" ht="19.5" customHeight="1" spans="3:238">
       <c r="C26" s="8">
         <v>10209</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>216</v>
+        <v>47</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G26" s="8">
         <v>10210</v>
@@ -2980,25 +3357,25 @@
         <v>8000000</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M26" s="11" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="ID26"/>
     </row>
-    <row r="27" spans="3:238" ht="19.5" customHeight="1">
+    <row r="27" ht="19.5" customHeight="1" spans="3:238">
       <c r="C27" s="8">
         <v>10210</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>216</v>
+        <v>47</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G27" s="8">
         <v>0</v>
@@ -3013,28 +3390,28 @@
         <v>126000</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="M27" s="11" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="ID27"/>
     </row>
-    <row r="28" spans="3:238" ht="22.5" customHeight="1">
+    <row r="28" ht="22.5" customHeight="1" spans="3:13">
       <c r="C28" s="8">
         <v>10300</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G28" s="8">
         <v>10301</v>
@@ -3052,22 +3429,22 @@
         <v>1000000</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M28" s="11"/>
     </row>
-    <row r="29" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="29" ht="20.1" customHeight="1" spans="3:13">
       <c r="C29" s="8">
         <v>10301</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G29" s="8">
         <v>10302</v>
@@ -3088,21 +3465,21 @@
         <v>26</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" ht="20.1" customHeight="1" spans="3:238">
       <c r="C30" s="8">
         <v>10302</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G30" s="8">
         <v>10303</v>
@@ -3120,25 +3497,25 @@
         <v>2000000</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="ID30"/>
     </row>
-    <row r="31" spans="3:238" ht="19.5" customHeight="1">
+    <row r="31" ht="19.5" customHeight="1" spans="3:238">
       <c r="C31" s="8">
         <v>10303</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G31" s="8">
         <v>10304</v>
@@ -3156,25 +3533,25 @@
         <v>2500000</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="ID31"/>
     </row>
-    <row r="32" spans="3:238" ht="19.5" customHeight="1">
+    <row r="32" ht="19.5" customHeight="1" spans="3:238">
       <c r="C32" s="8">
         <v>10304</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G32" s="8">
         <v>10305</v>
@@ -3192,25 +3569,25 @@
         <v>3000000</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="ID32"/>
     </row>
-    <row r="33" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="33" ht="20.1" customHeight="1" spans="3:13">
       <c r="C33" s="8">
         <v>10305</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G33" s="8">
         <v>10306</v>
@@ -3228,24 +3605,24 @@
         <v>4000000</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="34" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" ht="20.1" customHeight="1" spans="3:238">
       <c r="C34" s="8">
         <v>10306</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G34" s="8">
         <v>10307</v>
@@ -3263,25 +3640,25 @@
         <v>5000000</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M34" s="11" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="ID34"/>
     </row>
-    <row r="35" spans="3:238" ht="19.5" customHeight="1">
+    <row r="35" ht="19.5" customHeight="1" spans="3:238">
       <c r="C35" s="8">
         <v>10307</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G35" s="8">
         <v>10308</v>
@@ -3299,25 +3676,25 @@
         <v>6000000</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M35" s="11" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="ID35"/>
     </row>
-    <row r="36" spans="3:238" ht="19.5" customHeight="1">
+    <row r="36" ht="19.5" customHeight="1" spans="3:238">
       <c r="C36" s="8">
         <v>10308</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G36" s="8">
         <v>10309</v>
@@ -3335,25 +3712,25 @@
         <v>7000000</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="M36" s="11" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="ID36"/>
     </row>
-    <row r="37" spans="3:238" ht="19.5" customHeight="1">
+    <row r="37" ht="19.5" customHeight="1" spans="3:238">
       <c r="C37" s="8">
         <v>10309</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G37" s="8">
         <v>10310</v>
@@ -3371,25 +3748,25 @@
         <v>8000000</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M37" s="11" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="ID37"/>
     </row>
-    <row r="38" spans="3:238" ht="19.5" customHeight="1">
+    <row r="38" ht="19.5" customHeight="1" spans="3:238">
       <c r="C38" s="8">
         <v>10310</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G38" s="8">
         <v>0</v>
@@ -3404,28 +3781,28 @@
         <v>126000</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="M38" s="11" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="ID38"/>
     </row>
-    <row r="39" spans="3:238" ht="22.5" customHeight="1">
+    <row r="39" ht="22.5" customHeight="1" spans="3:13">
       <c r="C39" s="8">
         <v>10400</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G39" s="8">
         <v>10401</v>
@@ -3443,22 +3820,22 @@
         <v>1000000</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M39" s="11"/>
     </row>
-    <row r="40" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="40" ht="20.1" customHeight="1" spans="3:13">
       <c r="C40" s="8">
         <v>10401</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G40" s="8">
         <v>10402</v>
@@ -3479,21 +3856,21 @@
         <v>26</v>
       </c>
       <c r="M40" s="11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="41" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" ht="20.1" customHeight="1" spans="3:238">
       <c r="C41" s="8">
         <v>10402</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G41" s="8">
         <v>10403</v>
@@ -3511,25 +3888,25 @@
         <v>2000000</v>
       </c>
       <c r="L41" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M41" s="11" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="ID41"/>
     </row>
-    <row r="42" spans="3:238" ht="19.5" customHeight="1">
+    <row r="42" ht="19.5" customHeight="1" spans="3:238">
       <c r="C42" s="8">
         <v>10403</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G42" s="8">
         <v>10404</v>
@@ -3547,25 +3924,25 @@
         <v>2500000</v>
       </c>
       <c r="L42" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M42" s="11" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="ID42"/>
     </row>
-    <row r="43" spans="3:238" ht="19.5" customHeight="1">
+    <row r="43" ht="19.5" customHeight="1" spans="3:238">
       <c r="C43" s="8">
         <v>10404</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G43" s="8">
         <v>10405</v>
@@ -3583,25 +3960,25 @@
         <v>3000000</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M43" s="11" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="ID43"/>
     </row>
-    <row r="44" spans="3:238" ht="22.5" customHeight="1">
+    <row r="44" ht="22.5" customHeight="1" spans="3:13">
       <c r="C44" s="8">
         <v>10405</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G44" s="8">
         <v>10406</v>
@@ -3619,24 +3996,24 @@
         <v>4000000</v>
       </c>
       <c r="L44" s="10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M44" s="11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="45" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" ht="20.1" customHeight="1" spans="3:13">
       <c r="C45" s="8">
         <v>10406</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G45" s="8">
         <v>10407</v>
@@ -3654,24 +4031,24 @@
         <v>5000000</v>
       </c>
       <c r="L45" s="10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M45" s="11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="46" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" ht="20.1" customHeight="1" spans="3:238">
       <c r="C46" s="8">
         <v>10407</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G46" s="8">
         <v>10408</v>
@@ -3689,25 +4066,25 @@
         <v>6000000</v>
       </c>
       <c r="L46" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M46" s="11" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="ID46"/>
     </row>
-    <row r="47" spans="3:238" ht="19.5" customHeight="1">
+    <row r="47" ht="19.5" customHeight="1" spans="3:238">
       <c r="C47" s="8">
         <v>10408</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G47" s="8">
         <v>10409</v>
@@ -3725,25 +4102,25 @@
         <v>7000000</v>
       </c>
       <c r="L47" s="10" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="M47" s="11" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="ID47"/>
     </row>
-    <row r="48" spans="3:238" ht="19.5" customHeight="1">
+    <row r="48" ht="19.5" customHeight="1" spans="3:238">
       <c r="C48" s="8">
         <v>10409</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G48" s="8">
         <v>10410</v>
@@ -3761,25 +4138,25 @@
         <v>8000000</v>
       </c>
       <c r="L48" s="10" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M48" s="11" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="ID48"/>
     </row>
-    <row r="49" spans="3:238" ht="19.5" customHeight="1">
+    <row r="49" ht="19.5" customHeight="1" spans="3:238">
       <c r="C49" s="8">
         <v>10410</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G49" s="8">
         <v>0</v>
@@ -3794,28 +4171,28 @@
         <v>126000</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="L49" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="M49" s="11" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="ID49"/>
     </row>
-    <row r="50" spans="3:238" ht="22.5" customHeight="1">
+    <row r="50" ht="22.5" customHeight="1" spans="3:13">
       <c r="C50" s="8">
         <v>10500</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="G50" s="8">
         <v>10501</v>
@@ -3833,22 +4210,22 @@
         <v>1000000</v>
       </c>
       <c r="L50" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M50" s="11"/>
     </row>
-    <row r="51" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="51" ht="20.1" customHeight="1" spans="3:13">
       <c r="C51" s="8">
         <v>10501</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="G51" s="8">
         <v>10502</v>
@@ -3869,21 +4246,21 @@
         <v>26</v>
       </c>
       <c r="M51" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="52" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="52" ht="20.1" customHeight="1" spans="3:238">
       <c r="C52" s="8">
         <v>10502</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="G52" s="8">
         <v>10503</v>
@@ -3901,25 +4278,25 @@
         <v>2000000</v>
       </c>
       <c r="L52" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M52" s="11" t="s">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="ID52"/>
     </row>
-    <row r="53" spans="3:238" ht="19.5" customHeight="1">
+    <row r="53" ht="19.5" customHeight="1" spans="3:238">
       <c r="C53" s="8">
         <v>10503</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="G53" s="8">
         <v>10504</v>
@@ -3937,25 +4314,25 @@
         <v>2500000</v>
       </c>
       <c r="L53" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M53" s="11" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="ID53"/>
     </row>
-    <row r="54" spans="3:238" ht="19.5" customHeight="1">
+    <row r="54" ht="19.5" customHeight="1" spans="3:238">
       <c r="C54" s="8">
         <v>10504</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="G54" s="8">
         <v>10505</v>
@@ -3973,25 +4350,25 @@
         <v>3000000</v>
       </c>
       <c r="L54" s="10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M54" s="11" t="s">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="ID54"/>
     </row>
-    <row r="55" spans="3:238" ht="22.5" customHeight="1">
+    <row r="55" ht="22.5" customHeight="1" spans="3:13">
       <c r="C55" s="8">
         <v>10505</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="G55" s="8">
         <v>10506</v>
@@ -4009,24 +4386,24 @@
         <v>4000000</v>
       </c>
       <c r="L55" s="10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M55" s="11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="56" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" ht="20.1" customHeight="1" spans="3:13">
       <c r="C56" s="8">
         <v>10506</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="G56" s="8">
         <v>10507</v>
@@ -4044,24 +4421,24 @@
         <v>5000000</v>
       </c>
       <c r="L56" s="10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M56" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="57" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="57" ht="20.1" customHeight="1" spans="3:238">
       <c r="C57" s="8">
         <v>10507</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="G57" s="8">
         <v>10508</v>
@@ -4079,25 +4456,25 @@
         <v>6000000</v>
       </c>
       <c r="L57" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M57" s="11" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="ID57"/>
     </row>
-    <row r="58" spans="3:238" ht="19.5" customHeight="1">
+    <row r="58" ht="19.5" customHeight="1" spans="3:238">
       <c r="C58" s="8">
         <v>10508</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="G58" s="8">
         <v>10509</v>
@@ -4115,25 +4492,25 @@
         <v>7000000</v>
       </c>
       <c r="L58" s="10" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="M58" s="11" t="s">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="ID58"/>
     </row>
-    <row r="59" spans="3:238" ht="19.5" customHeight="1">
+    <row r="59" ht="19.5" customHeight="1" spans="3:238">
       <c r="C59" s="8">
         <v>10509</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="G59" s="8">
         <v>10510</v>
@@ -4151,25 +4528,25 @@
         <v>8000000</v>
       </c>
       <c r="L59" s="10" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M59" s="11" t="s">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="ID59"/>
     </row>
-    <row r="60" spans="3:238" ht="19.5" customHeight="1">
+    <row r="60" ht="19.5" customHeight="1" spans="3:238">
       <c r="C60" s="8">
         <v>10510</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="G60" s="8">
         <v>0</v>
@@ -4184,28 +4561,28 @@
         <v>126000</v>
       </c>
       <c r="K60" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="L60" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="M60" s="11" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="ID60"/>
     </row>
-    <row r="61" spans="3:238" ht="22.5" customHeight="1">
+    <row r="61" ht="22.5" customHeight="1" spans="3:13">
       <c r="C61" s="8">
         <v>10600</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>212</v>
+        <v>99</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="G61" s="8">
         <v>10601</v>
@@ -4223,22 +4600,22 @@
         <v>1000000</v>
       </c>
       <c r="L61" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M61" s="11"/>
     </row>
-    <row r="62" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="62" ht="20.1" customHeight="1" spans="3:13">
       <c r="C62" s="8">
         <v>10601</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>212</v>
+        <v>99</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="G62" s="8">
         <v>10602</v>
@@ -4259,21 +4636,21 @@
         <v>26</v>
       </c>
       <c r="M62" s="11" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="63" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="63" ht="20.1" customHeight="1" spans="3:238">
       <c r="C63" s="8">
         <v>10602</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>147</v>
+        <v>98</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>212</v>
+        <v>99</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="G63" s="8">
         <v>10603</v>
@@ -4291,25 +4668,25 @@
         <v>2000000</v>
       </c>
       <c r="L63" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M63" s="11" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="ID63"/>
     </row>
-    <row r="64" spans="3:238" ht="19.5" customHeight="1">
+    <row r="64" ht="19.5" customHeight="1" spans="3:238">
       <c r="C64" s="8">
         <v>10603</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>212</v>
+        <v>99</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="G64" s="8">
         <v>10604</v>
@@ -4327,25 +4704,25 @@
         <v>2500000</v>
       </c>
       <c r="L64" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M64" s="11" t="s">
-        <v>150</v>
+        <v>103</v>
       </c>
       <c r="ID64"/>
     </row>
-    <row r="65" spans="3:238" ht="19.5" customHeight="1">
+    <row r="65" ht="19.5" customHeight="1" spans="3:238">
       <c r="C65" s="8">
         <v>10604</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>212</v>
+        <v>99</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="G65" s="8">
         <v>10605</v>
@@ -4363,25 +4740,25 @@
         <v>3000000</v>
       </c>
       <c r="L65" s="10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M65" s="11" t="s">
-        <v>152</v>
+        <v>104</v>
       </c>
       <c r="ID65"/>
     </row>
-    <row r="66" spans="3:238" ht="22.5" customHeight="1">
+    <row r="66" ht="22.5" customHeight="1" spans="3:13">
       <c r="C66" s="8">
         <v>10605</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>212</v>
+        <v>99</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="G66" s="8">
         <v>10606</v>
@@ -4399,24 +4776,24 @@
         <v>4000000</v>
       </c>
       <c r="L66" s="10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M66" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="67" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="67" ht="20.1" customHeight="1" spans="3:13">
       <c r="C67" s="8">
         <v>10606</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>155</v>
+        <v>98</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>212</v>
+        <v>99</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="G67" s="8">
         <v>10607</v>
@@ -4434,24 +4811,24 @@
         <v>5000000</v>
       </c>
       <c r="L67" s="10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M67" s="11" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="68" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="68" ht="20.1" customHeight="1" spans="3:238">
       <c r="C68" s="8">
         <v>10607</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>157</v>
+        <v>98</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>212</v>
+        <v>99</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="G68" s="8">
         <v>10608</v>
@@ -4469,25 +4846,25 @@
         <v>6000000</v>
       </c>
       <c r="L68" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M68" s="11" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="ID68"/>
     </row>
-    <row r="69" spans="3:238" ht="19.5" customHeight="1">
+    <row r="69" ht="19.5" customHeight="1" spans="3:238">
       <c r="C69" s="8">
         <v>10608</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>212</v>
+        <v>99</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="G69" s="8">
         <v>10609</v>
@@ -4505,25 +4882,25 @@
         <v>7000000</v>
       </c>
       <c r="L69" s="10" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="M69" s="11" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="ID69"/>
     </row>
-    <row r="70" spans="3:238" ht="19.5" customHeight="1">
+    <row r="70" ht="19.5" customHeight="1" spans="3:238">
       <c r="C70" s="8">
         <v>10609</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>161</v>
+        <v>98</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>212</v>
+        <v>99</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="G70" s="8">
         <v>10610</v>
@@ -4541,25 +4918,25 @@
         <v>8000000</v>
       </c>
       <c r="L70" s="10" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M70" s="11" t="s">
-        <v>162</v>
+        <v>109</v>
       </c>
       <c r="ID70"/>
     </row>
-    <row r="71" spans="3:238" ht="19.5" customHeight="1">
+    <row r="71" ht="19.5" customHeight="1" spans="3:238">
       <c r="C71" s="8">
         <v>10610</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>163</v>
+        <v>98</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>212</v>
+        <v>99</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="G71" s="8">
         <v>0</v>
@@ -4574,28 +4951,28 @@
         <v>126000</v>
       </c>
       <c r="K71" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="L71" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="M71" s="11" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="ID71"/>
     </row>
-    <row r="72" spans="3:238" ht="22.5" customHeight="1">
+    <row r="72" ht="22.5" customHeight="1" spans="3:13">
       <c r="C72" s="8">
         <v>10700</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>213</v>
+        <v>112</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="G72" s="8">
         <v>10701</v>
@@ -4613,22 +4990,22 @@
         <v>1000000</v>
       </c>
       <c r="L72" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M72" s="11"/>
     </row>
-    <row r="73" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="73" ht="20.1" customHeight="1" spans="3:13">
       <c r="C73" s="8">
         <v>10701</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>167</v>
+        <v>111</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>213</v>
+        <v>112</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="G73" s="8">
         <v>10702</v>
@@ -4649,21 +5026,21 @@
         <v>26</v>
       </c>
       <c r="M73" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="74" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="74" ht="20.1" customHeight="1" spans="3:238">
       <c r="C74" s="8">
         <v>10702</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>213</v>
+        <v>112</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="G74" s="8">
         <v>10703</v>
@@ -4681,25 +5058,25 @@
         <v>2000000</v>
       </c>
       <c r="L74" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M74" s="11" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="ID74"/>
     </row>
-    <row r="75" spans="3:238" ht="19.5" customHeight="1">
+    <row r="75" ht="19.5" customHeight="1" spans="3:238">
       <c r="C75" s="8">
         <v>10703</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>213</v>
+        <v>112</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="G75" s="8">
         <v>10704</v>
@@ -4717,25 +5094,25 @@
         <v>2500000</v>
       </c>
       <c r="L75" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M75" s="11" t="s">
-        <v>172</v>
+        <v>116</v>
       </c>
       <c r="ID75"/>
     </row>
-    <row r="76" spans="3:238" ht="19.5" customHeight="1">
+    <row r="76" ht="19.5" customHeight="1" spans="3:238">
       <c r="C76" s="8">
         <v>10704</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>173</v>
+        <v>111</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>213</v>
+        <v>112</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="G76" s="8">
         <v>10705</v>
@@ -4753,25 +5130,25 @@
         <v>3000000</v>
       </c>
       <c r="L76" s="10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M76" s="11" t="s">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="ID76"/>
     </row>
-    <row r="77" spans="3:238" ht="22.5" customHeight="1">
+    <row r="77" ht="22.5" customHeight="1" spans="3:13">
       <c r="C77" s="8">
         <v>10705</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>213</v>
+        <v>112</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="G77" s="8">
         <v>10706</v>
@@ -4789,24 +5166,24 @@
         <v>4000000</v>
       </c>
       <c r="L77" s="10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M77" s="11" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="78" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="78" ht="20.1" customHeight="1" spans="3:13">
       <c r="C78" s="8">
         <v>10706</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>213</v>
+        <v>112</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="G78" s="8">
         <v>10707</v>
@@ -4824,24 +5201,24 @@
         <v>5000000</v>
       </c>
       <c r="L78" s="10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M78" s="11" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="79" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="79" ht="20.1" customHeight="1" spans="3:238">
       <c r="C79" s="8">
         <v>10707</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>179</v>
+        <v>111</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>213</v>
+        <v>112</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="G79" s="8">
         <v>10708</v>
@@ -4859,25 +5236,25 @@
         <v>6000000</v>
       </c>
       <c r="L79" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M79" s="11" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="ID79"/>
     </row>
-    <row r="80" spans="3:238" ht="19.5" customHeight="1">
+    <row r="80" ht="19.5" customHeight="1" spans="3:238">
       <c r="C80" s="8">
         <v>10708</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>181</v>
+        <v>111</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>213</v>
+        <v>112</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="G80" s="8">
         <v>10709</v>
@@ -4895,25 +5272,25 @@
         <v>7000000</v>
       </c>
       <c r="L80" s="10" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="M80" s="11" t="s">
-        <v>182</v>
+        <v>121</v>
       </c>
       <c r="ID80"/>
     </row>
-    <row r="81" spans="3:238" ht="19.5" customHeight="1">
+    <row r="81" ht="19.5" customHeight="1" spans="3:238">
       <c r="C81" s="8">
         <v>10709</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>183</v>
+        <v>111</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>213</v>
+        <v>112</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="G81" s="8">
         <v>10710</v>
@@ -4931,25 +5308,25 @@
         <v>8000000</v>
       </c>
       <c r="L81" s="10" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M81" s="11" t="s">
-        <v>184</v>
+        <v>122</v>
       </c>
       <c r="ID81"/>
     </row>
-    <row r="82" spans="3:238" ht="19.5" customHeight="1">
+    <row r="82" ht="19.5" customHeight="1" spans="3:238">
       <c r="C82" s="8">
         <v>10710</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>185</v>
+        <v>111</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>213</v>
+        <v>112</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="G82" s="8">
         <v>0</v>
@@ -4964,28 +5341,28 @@
         <v>126000</v>
       </c>
       <c r="K82" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="L82" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="M82" s="11" t="s">
-        <v>186</v>
+        <v>123</v>
       </c>
       <c r="ID82"/>
     </row>
-    <row r="83" spans="3:238" ht="22.5" customHeight="1">
+    <row r="83" ht="22.5" customHeight="1" spans="3:13">
       <c r="C83" s="8">
         <v>10800</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>187</v>
+        <v>124</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>214</v>
+        <v>125</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="G83" s="8">
         <v>10801</v>
@@ -5003,22 +5380,22 @@
         <v>1000000</v>
       </c>
       <c r="L83" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M83" s="11"/>
     </row>
-    <row r="84" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="84" ht="20.1" customHeight="1" spans="3:13">
       <c r="C84" s="8">
         <v>10801</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>189</v>
+        <v>124</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>214</v>
+        <v>125</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="G84" s="8">
         <v>10802</v>
@@ -5039,21 +5416,21 @@
         <v>26</v>
       </c>
       <c r="M84" s="11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="85" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="85" ht="20.1" customHeight="1" spans="3:238">
       <c r="C85" s="8">
         <v>10802</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>191</v>
+        <v>124</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>214</v>
+        <v>125</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="G85" s="8">
         <v>10803</v>
@@ -5071,25 +5448,25 @@
         <v>2000000</v>
       </c>
       <c r="L85" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M85" s="11" t="s">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="ID85"/>
     </row>
-    <row r="86" spans="3:238" ht="19.5" customHeight="1">
+    <row r="86" ht="19.5" customHeight="1" spans="3:238">
       <c r="C86" s="8">
         <v>10803</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>193</v>
+        <v>124</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>214</v>
+        <v>125</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="G86" s="8">
         <v>10804</v>
@@ -5107,25 +5484,25 @@
         <v>2500000</v>
       </c>
       <c r="L86" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M86" s="11" t="s">
-        <v>194</v>
+        <v>129</v>
       </c>
       <c r="ID86"/>
     </row>
-    <row r="87" spans="3:238" ht="19.5" customHeight="1">
+    <row r="87" ht="19.5" customHeight="1" spans="3:238">
       <c r="C87" s="8">
         <v>10804</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>195</v>
+        <v>124</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>214</v>
+        <v>125</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="G87" s="8">
         <v>10805</v>
@@ -5143,25 +5520,25 @@
         <v>3000000</v>
       </c>
       <c r="L87" s="10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M87" s="11" t="s">
-        <v>196</v>
+        <v>130</v>
       </c>
       <c r="ID87"/>
     </row>
-    <row r="88" spans="3:238" ht="22.5" customHeight="1">
+    <row r="88" ht="22.5" customHeight="1" spans="3:13">
       <c r="C88" s="8">
         <v>10805</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>214</v>
+        <v>125</v>
       </c>
       <c r="F88" s="10" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="G88" s="8">
         <v>10806</v>
@@ -5179,24 +5556,24 @@
         <v>4000000</v>
       </c>
       <c r="L88" s="10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M88" s="11" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="89" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="89" ht="20.1" customHeight="1" spans="3:13">
       <c r="C89" s="8">
         <v>10806</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>199</v>
+        <v>124</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>214</v>
+        <v>125</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="G89" s="8">
         <v>10807</v>
@@ -5214,24 +5591,24 @@
         <v>5000000</v>
       </c>
       <c r="L89" s="10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M89" s="11" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="90" spans="3:238" ht="20.100000000000001" customHeight="1">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="90" ht="20.1" customHeight="1" spans="3:238">
       <c r="C90" s="8">
         <v>10807</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>201</v>
+        <v>124</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>214</v>
+        <v>125</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="G90" s="8">
         <v>10808</v>
@@ -5249,25 +5626,25 @@
         <v>6000000</v>
       </c>
       <c r="L90" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M90" s="11" t="s">
-        <v>202</v>
+        <v>133</v>
       </c>
       <c r="ID90"/>
     </row>
-    <row r="91" spans="3:238" ht="19.5" customHeight="1">
+    <row r="91" ht="19.5" customHeight="1" spans="3:238">
       <c r="C91" s="8">
         <v>10808</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>203</v>
+        <v>124</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>214</v>
+        <v>125</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="G91" s="8">
         <v>10809</v>
@@ -5285,25 +5662,25 @@
         <v>7000000</v>
       </c>
       <c r="L91" s="10" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="M91" s="11" t="s">
-        <v>204</v>
+        <v>134</v>
       </c>
       <c r="ID91"/>
     </row>
-    <row r="92" spans="3:238" ht="19.5" customHeight="1">
+    <row r="92" ht="19.5" customHeight="1" spans="3:238">
       <c r="C92" s="8">
         <v>10809</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>205</v>
+        <v>124</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>214</v>
+        <v>125</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="G92" s="8">
         <v>10810</v>
@@ -5321,25 +5698,25 @@
         <v>8000000</v>
       </c>
       <c r="L92" s="10" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M92" s="11" t="s">
-        <v>206</v>
+        <v>135</v>
       </c>
       <c r="ID92"/>
     </row>
-    <row r="93" spans="3:238" ht="19.5" customHeight="1">
+    <row r="93" ht="19.5" customHeight="1" spans="3:238">
       <c r="C93" s="8">
         <v>10810</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>207</v>
+        <v>124</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>214</v>
+        <v>125</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="G93" s="8">
         <v>0</v>
@@ -5354,23 +5731,22 @@
         <v>126000</v>
       </c>
       <c r="K93" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="L93" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="M93" s="11" t="s">
-        <v>208</v>
+        <v>136</v>
       </c>
       <c r="ID93"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>